--- a/src/CleanArchitecture.Api/Templates/Excel/2026_1.4.07 Phu luc A TT03.2021- BC DTNN III-IV.xlsx
+++ b/src/CleanArchitecture.Api/Templates/Excel/2026_1.4.07 Phu luc A TT03.2021- BC DTNN III-IV.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\src\CleanArchitecture.Api\Templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\test\src\CleanArchitecture.Api\Templates\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD59A7B-F5E4-4821-AC4F-42F00F264136}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5582F1BF-113B-48C3-8422-F1F10138DF32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="5556" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="III.1" sheetId="42" r:id="rId1"/>
@@ -71,8 +71,8 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <customWorkbookViews>
+    <customWorkbookView name="PC - Personal View" guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" mergeInterval="0" personalView="1" maximized="1" showHorizontalScroll="0" showVerticalScroll="0" xWindow="-8" yWindow="-8" windowWidth="1376" windowHeight="744" activeSheetId="19"/>
     <customWorkbookView name="Pham Anh Thu - Personal View" guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" mergeInterval="0" personalView="1" maximized="1" xWindow="1" yWindow="1" windowWidth="1440" windowHeight="670" activeSheetId="10"/>
-    <customWorkbookView name="PC - Personal View" guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" mergeInterval="0" personalView="1" maximized="1" showHorizontalScroll="0" showVerticalScroll="0" xWindow="-8" yWindow="-8" windowWidth="1376" windowHeight="744" activeSheetId="19"/>
   </customWorkbookViews>
 </workbook>
 </file>
@@ -1705,89 +1705,9 @@
     <t>BÁO CÁO THỰC HIỆN DỰ ÁN ĐẦU TƯ</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Kính gửi: ................... </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(Tên cơ quan đăng ký đầu tư)</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">I. TỔ CHỨC KINH TẾ THỰC HIỆN DỰ ÁN </t>
   </si>
   <si>
-    <t>Tên tổ chức kinh tế thực hiện dự án đã được thành lập:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loại hình tổ chức kinh tế: </t>
-  </si>
-  <si>
-    <t>Địa chỉ trụ sở:</t>
-  </si>
-  <si>
-    <t>Mã số thuế:</t>
-  </si>
-  <si>
-    <r>
-      <t>Vốn điều lệ: .........</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (bằng chữ) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">đồng và tương đương ......... </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(bằng chữ)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> đô la Mỹ </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="13"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>(tỷ giá ...... ngày ...... của ......).</t>
-    </r>
-  </si>
-  <si>
     <t>Tỷ lệ góp vốn điều lệ của từng nhà đầu tư:</t>
   </si>
   <si>
@@ -1822,9 +1742,6 @@
   </si>
   <si>
     <t>Thông tin về người đại diện theo pháp luật:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Họ tên: ................................................................................. Giới tính: </t>
   </si>
   <si>
     <t>Mã số định danh cá nhân:</t>
@@ -2626,34 +2543,117 @@
     </r>
   </si>
   <si>
-    <t>Điện thoại: ......{{ProjectName}}..... Email: ...{{ProjectEmail}}..... Website: .......{{ProjectWebsite}}..................</t>
-  </si>
-  <si>
-    <t>{{Items.Name}}</t>
-  </si>
-  <si>
-    <t>{{Items.Nationality}}</t>
-  </si>
-  <si>
-    <t>{{Items.CapitalVND}}</t>
-  </si>
-  <si>
-    <t>{{Items.CapitalUSD}}</t>
-  </si>
-  <si>
-    <t>{{Items.Ratio}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ngày sinh: .................. Quốc tịch: .......{{ProjectWebsite}}............. Chức danh: {{ProjectWebsite}}  </t>
-  </si>
-  <si>
-    <t>{{Employees.Name}}</t>
-  </si>
-  <si>
-    <t>{{Employees.CodeVSIC}}</t>
-  </si>
-  <si>
-    <t>{{Employees.CodeCPC}}</t>
+    <r>
+      <t xml:space="preserve">Kính gửi: .......{{TenCoQuanDangKy}}............ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(Tên cơ quan đăng ký đầu tư)</t>
+    </r>
+  </si>
+  <si>
+    <t>Tên tổ chức kinh tế thực hiện dự án đã được thành lập: {{TenToChucKinhTe}}</t>
+  </si>
+  <si>
+    <t>Loại hình tổ chức kinh tế: {{LoaiHinhToChuc}}</t>
+  </si>
+  <si>
+    <t>Địa chỉ trụ sở: {{DiaChiTruSo}}</t>
+  </si>
+  <si>
+    <t>Mã số thuế: {{MST}}</t>
+  </si>
+  <si>
+    <t>Điện thoại: ......{{DienThoai}}..... Email: ...{{Email}}..... Website: .......{{WebSite}}..................</t>
+  </si>
+  <si>
+    <r>
+      <t>Vốn điều lệ: ....{{VonDieuLeVND}}.....</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> (bằng chữ) {{BangChuVND}} </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">đồng và tương đương ....{{VonDieuLeUSD}}..... </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(bằng chữ) {{BangChuUSD}}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve"> đô la Mỹ </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="13"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>(tỷ giá ...{{TyGia}}... ngày ...{{Ngay}}... của ...{{Cua}}...).</t>
+    </r>
+  </si>
+  <si>
+    <t>{{MucTieuHoatDongs.Ten}}</t>
+  </si>
+  <si>
+    <t>{{MucTieuHoatDongs.MaNganhCPC}}</t>
+  </si>
+  <si>
+    <t>{{MucTieuHoatDongs.MaNganhVSIC}}</t>
+  </si>
+  <si>
+    <t>{{NhaDauTus.Ten}}</t>
+  </si>
+  <si>
+    <t>{{NhaDauTus.QuocTich}}</t>
+  </si>
+  <si>
+    <t>{{NhaDauTus.VND}}</t>
+  </si>
+  <si>
+    <t>{{NhaDauTus.TuongDuongUSD}}</t>
+  </si>
+  <si>
+    <t>{{NhaDauTus.TyLe}}</t>
+  </si>
+  <si>
+    <t>Họ tên: .........{{HoTenNguoiDaiDienPL}}................. Giới tính: {{GioiTinh}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày sinh: .................. Quốc tịch: .................... Chức danh: {{ProjectWebsite}}  </t>
   </si>
 </sst>
 </file>
@@ -2952,7 +2952,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="82">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -4059,12 +4059,53 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="498">
+  <cellXfs count="507">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5214,9 +5255,6 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5234,6 +5272,63 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="4" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -5247,6 +5342,42 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -5262,13 +5393,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -5277,104 +5401,53 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="54" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="58" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="4" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="21" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="66" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="64" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -5383,40 +5456,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="68" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -5451,20 +5504,29 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5482,44 +5544,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5547,36 +5585,51 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5592,12 +5645,6 @@
     <xf numFmtId="3" fontId="10" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="71" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="10" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5608,13 +5655,13 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -5622,15 +5669,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -5655,6 +5693,26 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="82" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="83" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7216,92 +7274,92 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="375" t="s">
+      <c r="A1" s="398" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="375"/>
-      <c r="C1" s="375"/>
-      <c r="D1" s="375"/>
-      <c r="E1" s="375"/>
+      <c r="B1" s="398"/>
+      <c r="C1" s="398"/>
+      <c r="D1" s="398"/>
+      <c r="E1" s="398"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="375" t="s">
+      <c r="A3" s="398" t="s">
         <v>129</v>
       </c>
-      <c r="B3" s="375"/>
-      <c r="C3" s="375"/>
-      <c r="D3" s="375"/>
-      <c r="E3" s="375"/>
+      <c r="B3" s="398"/>
+      <c r="C3" s="398"/>
+      <c r="D3" s="398"/>
+      <c r="E3" s="398"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="375" t="s">
+      <c r="A4" s="398" t="s">
         <v>300</v>
       </c>
-      <c r="B4" s="375"/>
-      <c r="C4" s="375"/>
-      <c r="D4" s="375"/>
-      <c r="E4" s="375"/>
+      <c r="B4" s="398"/>
+      <c r="C4" s="398"/>
+      <c r="D4" s="398"/>
+      <c r="E4" s="398"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="376" t="s">
+      <c r="A5" s="399" t="s">
         <v>362</v>
       </c>
-      <c r="B5" s="376"/>
-      <c r="C5" s="376"/>
-      <c r="D5" s="376"/>
-      <c r="E5" s="376"/>
+      <c r="B5" s="399"/>
+      <c r="C5" s="399"/>
+      <c r="D5" s="399"/>
+      <c r="E5" s="399"/>
     </row>
     <row r="6" spans="1:19" ht="51.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="377" t="s">
+      <c r="A6" s="400" t="s">
         <v>219</v>
       </c>
-      <c r="B6" s="378"/>
-      <c r="C6" s="378"/>
-      <c r="D6" s="378"/>
-      <c r="E6" s="378"/>
+      <c r="B6" s="401"/>
+      <c r="C6" s="401"/>
+      <c r="D6" s="401"/>
+      <c r="E6" s="401"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="377"/>
-      <c r="B7" s="377"/>
-      <c r="C7" s="377"/>
-      <c r="D7" s="377"/>
-      <c r="E7" s="377"/>
+      <c r="A7" s="400"/>
+      <c r="B7" s="400"/>
+      <c r="C7" s="400"/>
+      <c r="D7" s="400"/>
+      <c r="E7" s="400"/>
     </row>
     <row r="8" spans="1:19" s="135" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="379" t="s">
+      <c r="A8" s="375" t="s">
         <v>228</v>
       </c>
-      <c r="B8" s="379"/>
-      <c r="C8" s="379"/>
-      <c r="D8" s="379" t="s">
+      <c r="B8" s="375"/>
+      <c r="C8" s="375"/>
+      <c r="D8" s="375" t="s">
         <v>357</v>
       </c>
-      <c r="E8" s="379"/>
+      <c r="E8" s="375"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A9" s="380"/>
-      <c r="B9" s="380"/>
-      <c r="C9" s="380"/>
-      <c r="D9" s="380"/>
-      <c r="E9" s="380"/>
+      <c r="A9" s="372"/>
+      <c r="B9" s="372"/>
+      <c r="C9" s="372"/>
+      <c r="D9" s="372"/>
+      <c r="E9" s="372"/>
     </row>
     <row r="10" spans="1:19" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="379" t="s">
+      <c r="A10" s="375" t="s">
         <v>144</v>
       </c>
-      <c r="B10" s="379"/>
-      <c r="C10" s="379"/>
-      <c r="D10" s="379"/>
-      <c r="E10" s="379"/>
+      <c r="B10" s="375"/>
+      <c r="C10" s="375"/>
+      <c r="D10" s="375"/>
+      <c r="E10" s="375"/>
     </row>
     <row r="11" spans="1:19" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A11" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="B11" s="381"/>
-      <c r="C11" s="381"/>
-      <c r="D11" s="381"/>
-      <c r="E11" s="382"/>
+      <c r="B11" s="402"/>
+      <c r="C11" s="402"/>
+      <c r="D11" s="402"/>
+      <c r="E11" s="403"/>
       <c r="F11" s="33"/>
       <c r="G11" s="33"/>
       <c r="H11" s="33"/>
@@ -7321,8 +7379,8 @@
       <c r="A12" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="372"/>
-      <c r="C12" s="373"/>
+      <c r="B12" s="386"/>
+      <c r="C12" s="387"/>
       <c r="D12" s="9" t="s">
         <v>61</v>
       </c>
@@ -7346,10 +7404,10 @@
       <c r="A13" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="B13" s="372"/>
-      <c r="C13" s="373"/>
-      <c r="D13" s="373"/>
-      <c r="E13" s="374"/>
+      <c r="B13" s="386"/>
+      <c r="C13" s="387"/>
+      <c r="D13" s="387"/>
+      <c r="E13" s="388"/>
       <c r="F13" s="33"/>
       <c r="G13" s="33"/>
       <c r="H13" s="33"/>
@@ -7369,10 +7427,10 @@
       <c r="A14" s="137" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="372"/>
-      <c r="C14" s="373"/>
-      <c r="D14" s="373"/>
-      <c r="E14" s="374"/>
+      <c r="B14" s="386"/>
+      <c r="C14" s="387"/>
+      <c r="D14" s="387"/>
+      <c r="E14" s="388"/>
       <c r="F14" s="33"/>
       <c r="G14" s="33"/>
       <c r="H14" s="33"/>
@@ -7392,10 +7450,10 @@
       <c r="A15" s="137" t="s">
         <v>64</v>
       </c>
-      <c r="B15" s="372"/>
-      <c r="C15" s="373"/>
-      <c r="D15" s="373"/>
-      <c r="E15" s="374"/>
+      <c r="B15" s="386"/>
+      <c r="C15" s="387"/>
+      <c r="D15" s="387"/>
+      <c r="E15" s="388"/>
       <c r="F15" s="33"/>
       <c r="G15" s="33"/>
       <c r="H15" s="33"/>
@@ -7415,10 +7473,10 @@
       <c r="A16" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="385"/>
-      <c r="C16" s="386"/>
-      <c r="D16" s="386"/>
-      <c r="E16" s="387"/>
+      <c r="B16" s="389"/>
+      <c r="C16" s="390"/>
+      <c r="D16" s="390"/>
+      <c r="E16" s="391"/>
       <c r="F16" s="33"/>
       <c r="G16" s="33"/>
       <c r="H16" s="33"/>
@@ -7438,8 +7496,8 @@
       <c r="A17" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="385"/>
-      <c r="C17" s="386"/>
+      <c r="B17" s="389"/>
+      <c r="C17" s="390"/>
       <c r="D17" s="11" t="s">
         <v>66</v>
       </c>
@@ -7463,10 +7521,10 @@
       <c r="A18" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="385"/>
-      <c r="C18" s="386"/>
-      <c r="D18" s="386"/>
-      <c r="E18" s="387"/>
+      <c r="B18" s="389"/>
+      <c r="C18" s="390"/>
+      <c r="D18" s="390"/>
+      <c r="E18" s="391"/>
       <c r="F18" s="33"/>
       <c r="G18" s="33"/>
       <c r="H18" s="33"/>
@@ -7486,10 +7544,10 @@
       <c r="A19" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="385"/>
-      <c r="C19" s="386"/>
-      <c r="D19" s="386"/>
-      <c r="E19" s="387"/>
+      <c r="B19" s="389"/>
+      <c r="C19" s="390"/>
+      <c r="D19" s="390"/>
+      <c r="E19" s="391"/>
       <c r="F19" s="33"/>
       <c r="G19" s="33"/>
       <c r="H19" s="33"/>
@@ -7509,8 +7567,8 @@
       <c r="A20" s="124" t="s">
         <v>68</v>
       </c>
-      <c r="B20" s="388"/>
-      <c r="C20" s="389"/>
+      <c r="B20" s="392"/>
+      <c r="C20" s="393"/>
       <c r="D20" s="13" t="s">
         <v>69</v>
       </c>
@@ -7554,13 +7612,13 @@
       <c r="S21" s="33"/>
     </row>
     <row r="22" spans="1:235" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="390" t="s">
+      <c r="A22" s="394" t="s">
         <v>143</v>
       </c>
-      <c r="B22" s="390"/>
-      <c r="C22" s="390"/>
-      <c r="D22" s="390"/>
-      <c r="E22" s="390"/>
+      <c r="B22" s="394"/>
+      <c r="C22" s="394"/>
+      <c r="D22" s="394"/>
+      <c r="E22" s="394"/>
       <c r="F22" s="33"/>
       <c r="G22" s="33"/>
       <c r="H22" s="33"/>
@@ -7879,11 +7937,11 @@
         <v>107</v>
       </c>
       <c r="B29" s="23"/>
-      <c r="C29" s="391" t="s">
+      <c r="C29" s="395" t="s">
         <v>83</v>
       </c>
-      <c r="D29" s="391"/>
-      <c r="E29" s="392"/>
+      <c r="D29" s="395"/>
+      <c r="E29" s="374"/>
     </row>
     <row r="30" spans="1:235" x14ac:dyDescent="0.3">
       <c r="A30" s="131" t="s">
@@ -7983,20 +8041,20 @@
         <v>96</v>
       </c>
       <c r="B39" s="23"/>
-      <c r="C39" s="383"/>
-      <c r="D39" s="383"/>
-      <c r="E39" s="384"/>
+      <c r="C39" s="384"/>
+      <c r="D39" s="384"/>
+      <c r="E39" s="385"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="130" t="s">
         <v>107</v>
       </c>
       <c r="B40" s="127"/>
-      <c r="C40" s="393" t="s">
+      <c r="C40" s="396" t="s">
         <v>83</v>
       </c>
-      <c r="D40" s="393"/>
-      <c r="E40" s="394"/>
+      <c r="D40" s="396"/>
+      <c r="E40" s="397"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="131" t="s">
@@ -8045,9 +8103,9 @@
         <v>95</v>
       </c>
       <c r="B45" s="127"/>
-      <c r="C45" s="383"/>
-      <c r="D45" s="383"/>
-      <c r="E45" s="384"/>
+      <c r="C45" s="384"/>
+      <c r="D45" s="384"/>
+      <c r="E45" s="385"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="141" t="s">
@@ -8122,7 +8180,7 @@
       </c>
       <c r="C52" s="24"/>
       <c r="D52" s="24"/>
-      <c r="E52" s="392" t="s">
+      <c r="E52" s="374" t="s">
         <v>83</v>
       </c>
     </row>
@@ -8135,7 +8193,7 @@
       </c>
       <c r="C53" s="24"/>
       <c r="D53" s="24"/>
-      <c r="E53" s="392"/>
+      <c r="E53" s="374"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="22" t="s">
@@ -8146,7 +8204,7 @@
       </c>
       <c r="C54" s="26"/>
       <c r="D54" s="26"/>
-      <c r="E54" s="392"/>
+      <c r="E54" s="374"/>
     </row>
     <row r="55" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A55" s="22" t="s">
@@ -8157,7 +8215,7 @@
       </c>
       <c r="C55" s="24"/>
       <c r="D55" s="28"/>
-      <c r="E55" s="392"/>
+      <c r="E55" s="374"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="129" t="s">
@@ -8167,10 +8225,10 @@
         <v>37</v>
       </c>
       <c r="C56" s="24"/>
-      <c r="D56" s="402" t="s">
+      <c r="D56" s="381" t="s">
         <v>83</v>
       </c>
-      <c r="E56" s="392"/>
+      <c r="E56" s="374"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="129" t="s">
@@ -8180,8 +8238,8 @@
         <v>37</v>
       </c>
       <c r="C57" s="24"/>
-      <c r="D57" s="403"/>
-      <c r="E57" s="392"/>
+      <c r="D57" s="382"/>
+      <c r="E57" s="374"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="351" t="s">
@@ -8189,8 +8247,8 @@
       </c>
       <c r="B58" s="353"/>
       <c r="C58" s="24"/>
-      <c r="D58" s="403"/>
-      <c r="E58" s="392"/>
+      <c r="D58" s="382"/>
+      <c r="E58" s="374"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="352" t="s">
@@ -8200,8 +8258,8 @@
         <v>379</v>
       </c>
       <c r="C59" s="24"/>
-      <c r="D59" s="403"/>
-      <c r="E59" s="392"/>
+      <c r="D59" s="382"/>
+      <c r="E59" s="374"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="352" t="s">
@@ -8211,8 +8269,8 @@
         <v>382</v>
       </c>
       <c r="C60" s="24"/>
-      <c r="D60" s="403"/>
-      <c r="E60" s="392"/>
+      <c r="D60" s="382"/>
+      <c r="E60" s="374"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="352" t="s">
@@ -8222,8 +8280,8 @@
         <v>384</v>
       </c>
       <c r="C61" s="24"/>
-      <c r="D61" s="403"/>
-      <c r="E61" s="392"/>
+      <c r="D61" s="382"/>
+      <c r="E61" s="374"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="352" t="s">
@@ -8233,8 +8291,8 @@
         <v>380</v>
       </c>
       <c r="C62" s="24"/>
-      <c r="D62" s="403"/>
-      <c r="E62" s="392"/>
+      <c r="D62" s="382"/>
+      <c r="E62" s="374"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="352" t="s">
@@ -8242,8 +8300,8 @@
       </c>
       <c r="B63" s="353"/>
       <c r="C63" s="24"/>
-      <c r="D63" s="404"/>
-      <c r="E63" s="392"/>
+      <c r="D63" s="383"/>
+      <c r="E63" s="374"/>
     </row>
     <row r="64" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A64" s="22" t="s">
@@ -8254,7 +8312,7 @@
       </c>
       <c r="C64" s="26"/>
       <c r="D64" s="26"/>
-      <c r="E64" s="392"/>
+      <c r="E64" s="374"/>
     </row>
     <row r="65" spans="1:5" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A65" s="134" t="s">
@@ -8275,22 +8333,22 @@
       <c r="E66" s="31"/>
     </row>
     <row r="67" spans="1:5" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="379" t="s">
+      <c r="A67" s="375" t="s">
         <v>145</v>
       </c>
-      <c r="B67" s="379"/>
-      <c r="C67" s="379"/>
-      <c r="D67" s="379"/>
-      <c r="E67" s="379"/>
+      <c r="B67" s="375"/>
+      <c r="C67" s="375"/>
+      <c r="D67" s="375"/>
+      <c r="E67" s="375"/>
     </row>
     <row r="68" spans="1:5" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="397" t="s">
+      <c r="A68" s="376" t="s">
         <v>146</v>
       </c>
-      <c r="B68" s="398"/>
-      <c r="C68" s="398"/>
-      <c r="D68" s="398"/>
-      <c r="E68" s="399"/>
+      <c r="B68" s="377"/>
+      <c r="C68" s="377"/>
+      <c r="D68" s="377"/>
+      <c r="E68" s="378"/>
     </row>
     <row r="69" spans="1:5" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B69" s="6"/>
@@ -8304,55 +8362,55 @@
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="395" t="s">
+      <c r="A71" s="371" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="400"/>
-      <c r="C71" s="400"/>
-      <c r="D71" s="400"/>
-      <c r="E71" s="400"/>
+      <c r="B71" s="379"/>
+      <c r="C71" s="379"/>
+      <c r="D71" s="379"/>
+      <c r="E71" s="379"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="401" t="s">
+      <c r="A72" s="380" t="s">
         <v>81</v>
       </c>
-      <c r="B72" s="401"/>
-      <c r="C72" s="401"/>
-      <c r="D72" s="401"/>
-      <c r="E72" s="401"/>
+      <c r="B72" s="380"/>
+      <c r="C72" s="380"/>
+      <c r="D72" s="380"/>
+      <c r="E72" s="380"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="401"/>
-      <c r="B73" s="401"/>
-      <c r="C73" s="401"/>
-      <c r="D73" s="401"/>
-      <c r="E73" s="401"/>
+      <c r="A73" s="380"/>
+      <c r="B73" s="380"/>
+      <c r="C73" s="380"/>
+      <c r="D73" s="380"/>
+      <c r="E73" s="380"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="395" t="s">
+      <c r="A74" s="371" t="s">
         <v>82</v>
       </c>
-      <c r="B74" s="395"/>
-      <c r="C74" s="395"/>
-      <c r="D74" s="395"/>
-      <c r="E74" s="395"/>
+      <c r="B74" s="371"/>
+      <c r="C74" s="371"/>
+      <c r="D74" s="371"/>
+      <c r="E74" s="371"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="136"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="C76" s="380" t="s">
+      <c r="C76" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="D76" s="380"/>
-      <c r="E76" s="380"/>
+      <c r="D76" s="372"/>
+      <c r="E76" s="372"/>
     </row>
     <row r="77" spans="1:5" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C77" s="396" t="s">
+      <c r="C77" s="373" t="s">
         <v>355</v>
       </c>
-      <c r="D77" s="396"/>
-      <c r="E77" s="396"/>
+      <c r="D77" s="373"/>
+      <c r="E77" s="373"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C78" s="32"/>
@@ -8393,27 +8451,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="C76:E76"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="E52:E64"/>
-    <mergeCell ref="A67:E67"/>
-    <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A71:E71"/>
-    <mergeCell ref="A72:E73"/>
-    <mergeCell ref="D56:D63"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C40:E40"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A3:E3"/>
@@ -8427,6 +8464,27 @@
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D8:E8"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="B15:E15"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="C76:E76"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="E52:E64"/>
+    <mergeCell ref="A67:E67"/>
+    <mergeCell ref="A68:E68"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A72:E73"/>
+    <mergeCell ref="D56:D63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
@@ -8462,117 +8520,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="447" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
-      <c r="H1" s="448"/>
-      <c r="I1" s="448"/>
-      <c r="J1" s="448"/>
-      <c r="K1" s="448"/>
-      <c r="L1" s="448"/>
-      <c r="M1" s="448"/>
-      <c r="N1" s="448"/>
-      <c r="O1" s="448"/>
-      <c r="P1" s="448"/>
-      <c r="Q1" s="448"/>
-      <c r="R1" s="448"/>
-      <c r="S1" s="448"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
+      <c r="H1" s="447"/>
+      <c r="I1" s="447"/>
+      <c r="J1" s="447"/>
+      <c r="K1" s="447"/>
+      <c r="L1" s="447"/>
+      <c r="M1" s="447"/>
+      <c r="N1" s="447"/>
+      <c r="O1" s="447"/>
+      <c r="P1" s="447"/>
+      <c r="Q1" s="447"/>
+      <c r="R1" s="447"/>
+      <c r="S1" s="447"/>
     </row>
     <row r="2" spans="1:19" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>377</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="448"/>
-      <c r="J2" s="448"/>
-      <c r="K2" s="448"/>
-      <c r="L2" s="448"/>
-      <c r="M2" s="448"/>
-      <c r="N2" s="448"/>
-      <c r="O2" s="448"/>
-      <c r="P2" s="448"/>
-      <c r="Q2" s="448"/>
-      <c r="R2" s="448"/>
-      <c r="S2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="447"/>
+      <c r="I2" s="447"/>
+      <c r="J2" s="447"/>
+      <c r="K2" s="447"/>
+      <c r="L2" s="447"/>
+      <c r="M2" s="447"/>
+      <c r="N2" s="447"/>
+      <c r="O2" s="447"/>
+      <c r="P2" s="447"/>
+      <c r="Q2" s="447"/>
+      <c r="R2" s="447"/>
+      <c r="S2" s="447"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="376" t="s">
+      <c r="A3" s="399" t="s">
         <v>263</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
-      <c r="E3" s="376"/>
-      <c r="F3" s="376"/>
-      <c r="G3" s="376"/>
-      <c r="H3" s="376"/>
-      <c r="I3" s="376"/>
-      <c r="J3" s="376"/>
-      <c r="K3" s="376"/>
-      <c r="L3" s="376"/>
-      <c r="M3" s="376"/>
-      <c r="N3" s="376"/>
-      <c r="O3" s="376"/>
-      <c r="P3" s="376"/>
-      <c r="Q3" s="376"/>
-      <c r="R3" s="376"/>
-      <c r="S3" s="376"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
+      <c r="G3" s="399"/>
+      <c r="H3" s="399"/>
+      <c r="I3" s="399"/>
+      <c r="J3" s="399"/>
+      <c r="K3" s="399"/>
+      <c r="L3" s="399"/>
+      <c r="M3" s="399"/>
+      <c r="N3" s="399"/>
+      <c r="O3" s="399"/>
+      <c r="P3" s="399"/>
+      <c r="Q3" s="399"/>
+      <c r="R3" s="399"/>
+      <c r="S3" s="399"/>
     </row>
     <row r="4" spans="1:19" s="180" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
-      <c r="I4" s="377"/>
-      <c r="J4" s="377"/>
-      <c r="K4" s="377"/>
-      <c r="L4" s="377"/>
-      <c r="M4" s="377"/>
-      <c r="N4" s="377"/>
-      <c r="O4" s="377"/>
-      <c r="P4" s="377"/>
-      <c r="Q4" s="377"/>
-      <c r="R4" s="377"/>
-      <c r="S4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
+      <c r="J4" s="400"/>
+      <c r="K4" s="400"/>
+      <c r="L4" s="400"/>
+      <c r="M4" s="400"/>
+      <c r="N4" s="400"/>
+      <c r="O4" s="400"/>
+      <c r="P4" s="400"/>
+      <c r="Q4" s="400"/>
+      <c r="R4" s="400"/>
+      <c r="S4" s="400"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="482"/>
-      <c r="B5" s="482"/>
-      <c r="C5" s="482"/>
-      <c r="D5" s="482"/>
-      <c r="E5" s="482"/>
-      <c r="F5" s="482"/>
-      <c r="G5" s="482"/>
-      <c r="H5" s="482"/>
-      <c r="I5" s="482"/>
-      <c r="J5" s="482"/>
-      <c r="K5" s="482"/>
-      <c r="L5" s="482"/>
-      <c r="M5" s="482"/>
-      <c r="N5" s="482"/>
-      <c r="O5" s="482"/>
-      <c r="P5" s="482"/>
-      <c r="Q5" s="482"/>
-      <c r="R5" s="482"/>
-      <c r="S5" s="482"/>
+      <c r="A5" s="474"/>
+      <c r="B5" s="474"/>
+      <c r="C5" s="474"/>
+      <c r="D5" s="474"/>
+      <c r="E5" s="474"/>
+      <c r="F5" s="474"/>
+      <c r="G5" s="474"/>
+      <c r="H5" s="474"/>
+      <c r="I5" s="474"/>
+      <c r="J5" s="474"/>
+      <c r="K5" s="474"/>
+      <c r="L5" s="474"/>
+      <c r="M5" s="474"/>
+      <c r="N5" s="474"/>
+      <c r="O5" s="474"/>
+      <c r="P5" s="474"/>
+      <c r="Q5" s="474"/>
+      <c r="R5" s="474"/>
+      <c r="S5" s="474"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="274"/>
@@ -8596,29 +8654,29 @@
       <c r="S6" s="274"/>
     </row>
     <row r="7" spans="1:19" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="449" t="s">
+      <c r="A7" s="448" t="s">
         <v>329</v>
       </c>
-      <c r="B7" s="449"/>
-      <c r="C7" s="449"/>
-      <c r="D7" s="449"/>
-      <c r="E7" s="449"/>
-      <c r="F7" s="449"/>
-      <c r="G7" s="449"/>
-      <c r="H7" s="449"/>
-      <c r="I7" s="449"/>
-      <c r="J7" s="449"/>
-      <c r="K7" s="449"/>
-      <c r="L7" s="449" t="s">
+      <c r="B7" s="448"/>
+      <c r="C7" s="448"/>
+      <c r="D7" s="448"/>
+      <c r="E7" s="448"/>
+      <c r="F7" s="448"/>
+      <c r="G7" s="448"/>
+      <c r="H7" s="448"/>
+      <c r="I7" s="448"/>
+      <c r="J7" s="448"/>
+      <c r="K7" s="448"/>
+      <c r="L7" s="448" t="s">
         <v>330</v>
       </c>
-      <c r="M7" s="449"/>
-      <c r="N7" s="449"/>
-      <c r="O7" s="449"/>
-      <c r="P7" s="449"/>
-      <c r="Q7" s="449"/>
-      <c r="R7" s="449"/>
-      <c r="S7" s="449"/>
+      <c r="M7" s="448"/>
+      <c r="N7" s="448"/>
+      <c r="O7" s="448"/>
+      <c r="P7" s="448"/>
+      <c r="Q7" s="448"/>
+      <c r="R7" s="448"/>
+      <c r="S7" s="448"/>
     </row>
     <row r="8" spans="1:19" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="274"/>
@@ -8642,113 +8700,113 @@
       <c r="S8" s="274"/>
     </row>
     <row r="9" spans="1:19" s="39" customFormat="1" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="479" t="s">
+      <c r="A9" s="481" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="477" t="s">
+      <c r="B9" s="472" t="s">
         <v>326</v>
       </c>
-      <c r="C9" s="477" t="s">
+      <c r="C9" s="472" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="483" t="s">
+      <c r="D9" s="468" t="s">
         <v>119</v>
       </c>
-      <c r="E9" s="477" t="s">
+      <c r="E9" s="472" t="s">
         <v>14</v>
       </c>
-      <c r="F9" s="483" t="s">
+      <c r="F9" s="468" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="483"/>
-      <c r="H9" s="483"/>
-      <c r="I9" s="477" t="s">
+      <c r="G9" s="468"/>
+      <c r="H9" s="468"/>
+      <c r="I9" s="472" t="s">
         <v>291</v>
       </c>
-      <c r="J9" s="477" t="s">
+      <c r="J9" s="472" t="s">
         <v>120</v>
       </c>
-      <c r="K9" s="477" t="s">
+      <c r="K9" s="472" t="s">
         <v>160</v>
       </c>
-      <c r="L9" s="477" t="s">
+      <c r="L9" s="472" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="483" t="s">
+      <c r="M9" s="468" t="s">
         <v>4</v>
       </c>
-      <c r="N9" s="483"/>
-      <c r="O9" s="483"/>
-      <c r="P9" s="483" t="s">
+      <c r="N9" s="468"/>
+      <c r="O9" s="468"/>
+      <c r="P9" s="468" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="483"/>
-      <c r="R9" s="477" t="s">
+      <c r="Q9" s="468"/>
+      <c r="R9" s="472" t="s">
         <v>292</v>
       </c>
-      <c r="S9" s="474" t="s">
+      <c r="S9" s="478" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:19" s="39" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="480"/>
-      <c r="B10" s="478"/>
-      <c r="C10" s="478"/>
-      <c r="D10" s="478"/>
-      <c r="E10" s="478"/>
-      <c r="F10" s="472" t="s">
+      <c r="A10" s="482"/>
+      <c r="B10" s="469"/>
+      <c r="C10" s="469"/>
+      <c r="D10" s="469"/>
+      <c r="E10" s="469"/>
+      <c r="F10" s="476" t="s">
         <v>7</v>
       </c>
-      <c r="G10" s="473"/>
-      <c r="H10" s="470" t="s">
+      <c r="G10" s="477"/>
+      <c r="H10" s="475" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="478"/>
-      <c r="J10" s="478"/>
-      <c r="K10" s="478"/>
-      <c r="L10" s="478"/>
-      <c r="M10" s="469" t="s">
+      <c r="I10" s="469"/>
+      <c r="J10" s="469"/>
+      <c r="K10" s="469"/>
+      <c r="L10" s="469"/>
+      <c r="M10" s="473" t="s">
         <v>9</v>
       </c>
-      <c r="N10" s="469" t="s">
+      <c r="N10" s="473" t="s">
         <v>10</v>
       </c>
-      <c r="O10" s="469" t="s">
+      <c r="O10" s="473" t="s">
         <v>11</v>
       </c>
-      <c r="P10" s="469" t="s">
+      <c r="P10" s="473" t="s">
         <v>9</v>
       </c>
-      <c r="Q10" s="469" t="s">
+      <c r="Q10" s="473" t="s">
         <v>10</v>
       </c>
-      <c r="R10" s="478"/>
-      <c r="S10" s="475"/>
+      <c r="R10" s="469"/>
+      <c r="S10" s="479"/>
     </row>
     <row r="11" spans="1:19" s="39" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="481"/>
-      <c r="B11" s="471"/>
-      <c r="C11" s="471"/>
-      <c r="D11" s="471"/>
-      <c r="E11" s="471"/>
+      <c r="A11" s="483"/>
+      <c r="B11" s="470"/>
+      <c r="C11" s="470"/>
+      <c r="D11" s="470"/>
+      <c r="E11" s="470"/>
       <c r="F11" s="152" t="s">
         <v>327</v>
       </c>
       <c r="G11" s="152" t="s">
         <v>328</v>
       </c>
-      <c r="H11" s="471"/>
-      <c r="I11" s="471"/>
-      <c r="J11" s="471"/>
-      <c r="K11" s="471"/>
-      <c r="L11" s="471"/>
-      <c r="M11" s="445"/>
-      <c r="N11" s="445"/>
-      <c r="O11" s="445"/>
-      <c r="P11" s="445"/>
-      <c r="Q11" s="445"/>
-      <c r="R11" s="471"/>
-      <c r="S11" s="476"/>
+      <c r="H11" s="470"/>
+      <c r="I11" s="470"/>
+      <c r="J11" s="470"/>
+      <c r="K11" s="470"/>
+      <c r="L11" s="470"/>
+      <c r="M11" s="439"/>
+      <c r="N11" s="439"/>
+      <c r="O11" s="439"/>
+      <c r="P11" s="439"/>
+      <c r="Q11" s="439"/>
+      <c r="R11" s="470"/>
+      <c r="S11" s="480"/>
     </row>
     <row r="12" spans="1:19" s="275" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="42">
@@ -8902,73 +8960,73 @@
       <c r="H17" s="279"/>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A18" s="457" t="s">
+      <c r="A18" s="456" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="457"/>
-      <c r="C18" s="457"/>
-      <c r="D18" s="457"/>
-      <c r="E18" s="457"/>
-      <c r="F18" s="457"/>
-      <c r="G18" s="457"/>
-      <c r="H18" s="457"/>
-      <c r="I18" s="457"/>
-      <c r="J18" s="457"/>
-      <c r="K18" s="457"/>
-      <c r="L18" s="457"/>
-      <c r="M18" s="457"/>
-      <c r="N18" s="457"/>
-      <c r="O18" s="457"/>
-      <c r="P18" s="457"/>
-      <c r="Q18" s="457"/>
-      <c r="R18" s="457"/>
-      <c r="S18" s="457"/>
+      <c r="B18" s="456"/>
+      <c r="C18" s="456"/>
+      <c r="D18" s="456"/>
+      <c r="E18" s="456"/>
+      <c r="F18" s="456"/>
+      <c r="G18" s="456"/>
+      <c r="H18" s="456"/>
+      <c r="I18" s="456"/>
+      <c r="J18" s="456"/>
+      <c r="K18" s="456"/>
+      <c r="L18" s="456"/>
+      <c r="M18" s="456"/>
+      <c r="N18" s="456"/>
+      <c r="O18" s="456"/>
+      <c r="P18" s="456"/>
+      <c r="Q18" s="456"/>
+      <c r="R18" s="456"/>
+      <c r="S18" s="456"/>
     </row>
     <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="280"/>
-      <c r="B19" s="484" t="s">
+      <c r="B19" s="471" t="s">
         <v>343</v>
       </c>
-      <c r="C19" s="484"/>
-      <c r="D19" s="484"/>
-      <c r="E19" s="484"/>
-      <c r="F19" s="484"/>
-      <c r="G19" s="484"/>
-      <c r="H19" s="484"/>
-      <c r="I19" s="484"/>
-      <c r="J19" s="484"/>
-      <c r="K19" s="484"/>
-      <c r="L19" s="484"/>
-      <c r="M19" s="484"/>
-      <c r="N19" s="484"/>
-      <c r="O19" s="484"/>
-      <c r="P19" s="484"/>
-      <c r="Q19" s="484"/>
-      <c r="R19" s="484"/>
-      <c r="S19" s="484"/>
+      <c r="C19" s="471"/>
+      <c r="D19" s="471"/>
+      <c r="E19" s="471"/>
+      <c r="F19" s="471"/>
+      <c r="G19" s="471"/>
+      <c r="H19" s="471"/>
+      <c r="I19" s="471"/>
+      <c r="J19" s="471"/>
+      <c r="K19" s="471"/>
+      <c r="L19" s="471"/>
+      <c r="M19" s="471"/>
+      <c r="N19" s="471"/>
+      <c r="O19" s="471"/>
+      <c r="P19" s="471"/>
+      <c r="Q19" s="471"/>
+      <c r="R19" s="471"/>
+      <c r="S19" s="471"/>
     </row>
     <row r="20" spans="1:19" s="93" customFormat="1" x14ac:dyDescent="0.3">
       <c r="E20" s="39"/>
       <c r="F20" s="279"/>
       <c r="G20" s="279"/>
       <c r="H20" s="279"/>
-      <c r="O20" s="380" t="s">
+      <c r="O20" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="P20" s="380"/>
-      <c r="Q20" s="380"/>
-      <c r="R20" s="380"/>
-      <c r="S20" s="380"/>
+      <c r="P20" s="372"/>
+      <c r="Q20" s="372"/>
+      <c r="R20" s="372"/>
+      <c r="S20" s="372"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="E21" s="173"/>
-      <c r="O21" s="448" t="s">
+      <c r="O21" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="P21" s="448"/>
-      <c r="Q21" s="448"/>
-      <c r="R21" s="448"/>
-      <c r="S21" s="448"/>
+      <c r="P21" s="447"/>
+      <c r="Q21" s="447"/>
+      <c r="R21" s="447"/>
+      <c r="S21" s="447"/>
     </row>
     <row r="22" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O22" s="451" t="s">
@@ -9001,7 +9059,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="B1">
+    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="B1">
       <selection activeCell="C23" sqref="C23"/>
       <pageMargins left="0.2" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="75" firstPageNumber="75" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -9009,7 +9067,7 @@
         <oddFooter>&amp;R&amp;P</oddFooter>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="B1">
+    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="B1">
       <selection activeCell="C23" sqref="C23"/>
       <pageMargins left="0.2" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="75" firstPageNumber="75" orientation="landscape" useFirstPageNumber="1" r:id="rId2"/>
@@ -9019,23 +9077,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="33">
-    <mergeCell ref="O21:S21"/>
-    <mergeCell ref="O22:S22"/>
-    <mergeCell ref="D9:D11"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="B19:S19"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="E9:E11"/>
-    <mergeCell ref="F9:H9"/>
-    <mergeCell ref="P9:Q9"/>
-    <mergeCell ref="M10:M11"/>
-    <mergeCell ref="I9:I11"/>
-    <mergeCell ref="P10:P11"/>
-    <mergeCell ref="A3:S3"/>
-    <mergeCell ref="A5:S5"/>
-    <mergeCell ref="A1:S1"/>
-    <mergeCell ref="A2:S2"/>
-    <mergeCell ref="A4:S4"/>
     <mergeCell ref="A7:K7"/>
     <mergeCell ref="L7:S7"/>
     <mergeCell ref="A18:S18"/>
@@ -9052,6 +9093,23 @@
     <mergeCell ref="B9:B11"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="C9:C11"/>
+    <mergeCell ref="A3:S3"/>
+    <mergeCell ref="A5:S5"/>
+    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A2:S2"/>
+    <mergeCell ref="A4:S4"/>
+    <mergeCell ref="O21:S21"/>
+    <mergeCell ref="O22:S22"/>
+    <mergeCell ref="D9:D11"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="B19:S19"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="E9:E11"/>
+    <mergeCell ref="F9:H9"/>
+    <mergeCell ref="P9:Q9"/>
+    <mergeCell ref="M10:M11"/>
+    <mergeCell ref="I9:I11"/>
+    <mergeCell ref="P10:P11"/>
   </mergeCells>
   <pageMargins left="0.98425196850393704" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="90" firstPageNumber="165" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId3"/>
@@ -9079,17 +9137,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>135</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
-      <c r="E1" s="440"/>
-      <c r="F1" s="440"/>
-      <c r="G1" s="440"/>
-      <c r="H1" s="440"/>
-      <c r="I1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
+      <c r="H1" s="434"/>
+      <c r="I1" s="434"/>
       <c r="J1" s="69"/>
       <c r="K1" s="69"/>
       <c r="L1" s="69"/>
@@ -9102,45 +9160,45 @@
       <c r="S1" s="69"/>
     </row>
     <row r="2" spans="1:19" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>331</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="447"/>
+      <c r="I2" s="447"/>
       <c r="J2" s="93"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="441" t="s">
+      <c r="A3" s="435" t="s">
         <v>262</v>
       </c>
-      <c r="B3" s="441"/>
-      <c r="C3" s="441"/>
-      <c r="D3" s="441"/>
-      <c r="E3" s="441"/>
-      <c r="F3" s="441"/>
-      <c r="G3" s="441"/>
-      <c r="H3" s="441"/>
-      <c r="I3" s="441"/>
+      <c r="B3" s="435"/>
+      <c r="C3" s="435"/>
+      <c r="D3" s="435"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="435"/>
+      <c r="I3" s="435"/>
       <c r="J3" s="251"/>
     </row>
     <row r="4" spans="1:19" s="37" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
-      <c r="I4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
       <c r="J4" s="34"/>
       <c r="K4" s="34"/>
       <c r="L4" s="34"/>
@@ -9153,15 +9211,15 @@
       <c r="S4" s="34"/>
     </row>
     <row r="5" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="487"/>
-      <c r="B5" s="487"/>
-      <c r="C5" s="487"/>
-      <c r="D5" s="487"/>
-      <c r="E5" s="487"/>
-      <c r="F5" s="487"/>
-      <c r="G5" s="487"/>
-      <c r="H5" s="487"/>
-      <c r="I5" s="487"/>
+      <c r="A5" s="484"/>
+      <c r="B5" s="484"/>
+      <c r="C5" s="484"/>
+      <c r="D5" s="484"/>
+      <c r="E5" s="484"/>
+      <c r="F5" s="484"/>
+      <c r="G5" s="484"/>
+      <c r="H5" s="484"/>
+      <c r="I5" s="484"/>
       <c r="J5" s="94"/>
       <c r="K5" s="94"/>
       <c r="L5" s="94"/>
@@ -9174,19 +9232,19 @@
       <c r="S5" s="94"/>
     </row>
     <row r="6" spans="1:19" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="449" t="s">
+      <c r="A6" s="448" t="s">
         <v>329</v>
       </c>
-      <c r="B6" s="449"/>
-      <c r="C6" s="449"/>
-      <c r="D6" s="449"/>
-      <c r="E6" s="449"/>
-      <c r="F6" s="449"/>
-      <c r="G6" s="449" t="s">
+      <c r="B6" s="448"/>
+      <c r="C6" s="448"/>
+      <c r="D6" s="448"/>
+      <c r="E6" s="448"/>
+      <c r="F6" s="448"/>
+      <c r="G6" s="448" t="s">
         <v>330</v>
       </c>
-      <c r="H6" s="449"/>
-      <c r="I6" s="449"/>
+      <c r="H6" s="448"/>
+      <c r="I6" s="448"/>
     </row>
     <row r="7" spans="1:19" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="94"/>
@@ -9210,46 +9268,46 @@
       <c r="S7" s="94"/>
     </row>
     <row r="8" spans="1:19" s="69" customFormat="1" ht="18.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="488" t="s">
+      <c r="A8" s="485" t="s">
         <v>87</v>
       </c>
-      <c r="B8" s="483" t="s">
+      <c r="B8" s="468" t="s">
         <v>261</v>
       </c>
-      <c r="C8" s="483" t="s">
+      <c r="C8" s="468" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="483" t="s">
+      <c r="D8" s="468" t="s">
         <v>119</v>
       </c>
-      <c r="E8" s="483" t="s">
+      <c r="E8" s="468" t="s">
         <v>47</v>
       </c>
-      <c r="F8" s="483" t="s">
+      <c r="F8" s="468" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="483" t="s">
+      <c r="G8" s="468" t="s">
         <v>121</v>
       </c>
-      <c r="H8" s="483"/>
-      <c r="I8" s="489" t="s">
+      <c r="H8" s="468"/>
+      <c r="I8" s="486" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="69" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="443"/>
-      <c r="B9" s="437"/>
-      <c r="C9" s="437"/>
-      <c r="D9" s="437"/>
-      <c r="E9" s="437"/>
-      <c r="F9" s="437"/>
+      <c r="A9" s="437"/>
+      <c r="B9" s="444"/>
+      <c r="C9" s="444"/>
+      <c r="D9" s="444"/>
+      <c r="E9" s="444"/>
+      <c r="F9" s="444"/>
       <c r="G9" s="40" t="s">
         <v>332</v>
       </c>
       <c r="H9" s="40" t="s">
         <v>333</v>
       </c>
-      <c r="I9" s="439"/>
+      <c r="I9" s="446"/>
     </row>
     <row r="10" spans="1:19" s="272" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="42">
@@ -9328,57 +9386,57 @@
     </row>
     <row r="15" spans="1:19" s="69" customFormat="1" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="485" t="s">
+      <c r="A16" s="487" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="485"/>
-      <c r="C16" s="485"/>
-      <c r="D16" s="485"/>
-      <c r="E16" s="485"/>
-      <c r="F16" s="485"/>
-      <c r="G16" s="485"/>
-      <c r="H16" s="485"/>
-      <c r="I16" s="485"/>
+      <c r="B16" s="487"/>
+      <c r="C16" s="487"/>
+      <c r="D16" s="487"/>
+      <c r="E16" s="487"/>
+      <c r="F16" s="487"/>
+      <c r="G16" s="487"/>
+      <c r="H16" s="487"/>
+      <c r="I16" s="487"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="273"/>
-      <c r="B17" s="486" t="s">
+      <c r="B17" s="488" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="486"/>
-      <c r="D17" s="486"/>
-      <c r="E17" s="486"/>
-      <c r="F17" s="486"/>
-      <c r="G17" s="486"/>
-      <c r="H17" s="486"/>
-      <c r="I17" s="486"/>
+      <c r="C17" s="488"/>
+      <c r="D17" s="488"/>
+      <c r="E17" s="488"/>
+      <c r="F17" s="488"/>
+      <c r="G17" s="488"/>
+      <c r="H17" s="488"/>
+      <c r="I17" s="488"/>
     </row>
     <row r="18" spans="1:9" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D18" s="35"/>
       <c r="E18" s="35"/>
       <c r="F18" s="251"/>
-      <c r="G18" s="435" t="s">
+      <c r="G18" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="H18" s="435"/>
-      <c r="I18" s="435"/>
+      <c r="H18" s="442"/>
+      <c r="I18" s="442"/>
     </row>
     <row r="19" spans="1:9" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D19" s="4"/>
       <c r="E19" s="54"/>
-      <c r="G19" s="440" t="s">
+      <c r="G19" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="440"/>
-      <c r="I19" s="440"/>
+      <c r="H19" s="434"/>
+      <c r="I19" s="434"/>
     </row>
     <row r="20" spans="1:9" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="F20" s="37"/>
-      <c r="G20" s="429" t="s">
+      <c r="G20" s="433" t="s">
         <v>297</v>
       </c>
-      <c r="H20" s="429"/>
-      <c r="I20" s="429"/>
+      <c r="H20" s="433"/>
+      <c r="I20" s="433"/>
     </row>
     <row r="21" spans="1:9" s="69" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -9389,7 +9447,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="F18" sqref="F18"/>
       <pageMargins left="1.1000000000000001" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="76" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -9397,7 +9455,7 @@
         <oddFooter>&amp;R&amp;P</oddFooter>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="F18" sqref="F18"/>
       <pageMargins left="1.1000000000000001" right="0.2" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="76" orientation="landscape" useFirstPageNumber="1" r:id="rId2"/>
@@ -9407,6 +9465,15 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="20">
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="A16:I16"/>
+    <mergeCell ref="B17:I17"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="A5:I5"/>
     <mergeCell ref="G20:I20"/>
@@ -9418,15 +9485,6 @@
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="G8:H8"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A4:I4"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="A16:I16"/>
-    <mergeCell ref="B17:I17"/>
   </mergeCells>
   <pageMargins left="1.1811023622047245" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="166" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId3"/>
@@ -9454,54 +9512,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="447" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
-      <c r="H1" s="448"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
+      <c r="H1" s="447"/>
       <c r="I1" s="93"/>
       <c r="J1" s="93"/>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>334</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="447"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="372" t="s">
         <v>263</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380"/>
-      <c r="F3" s="380"/>
-      <c r="G3" s="380"/>
-      <c r="H3" s="380"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
+      <c r="G3" s="372"/>
+      <c r="H3" s="372"/>
     </row>
     <row r="4" spans="1:19" s="180" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
       <c r="I4" s="34"/>
       <c r="J4" s="34"/>
       <c r="K4" s="34"/>
@@ -9515,14 +9573,14 @@
       <c r="S4" s="34"/>
     </row>
     <row r="5" spans="1:19" s="180" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="377"/>
-      <c r="B5" s="377"/>
-      <c r="C5" s="377"/>
-      <c r="D5" s="377"/>
-      <c r="E5" s="377"/>
-      <c r="F5" s="377"/>
-      <c r="G5" s="377"/>
-      <c r="H5" s="377"/>
+      <c r="A5" s="400"/>
+      <c r="B5" s="400"/>
+      <c r="C5" s="400"/>
+      <c r="D5" s="400"/>
+      <c r="E5" s="400"/>
+      <c r="F5" s="400"/>
+      <c r="G5" s="400"/>
+      <c r="H5" s="400"/>
       <c r="I5" s="34"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
@@ -9557,28 +9615,28 @@
       <c r="S6" s="34"/>
     </row>
     <row r="7" spans="1:19" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="449" t="s">
+      <c r="A7" s="448" t="s">
         <v>329</v>
       </c>
-      <c r="B7" s="449"/>
-      <c r="C7" s="449"/>
-      <c r="D7" s="449"/>
-      <c r="E7" s="449"/>
-      <c r="F7" s="449"/>
-      <c r="G7" s="449" t="s">
+      <c r="B7" s="448"/>
+      <c r="C7" s="448"/>
+      <c r="D7" s="448"/>
+      <c r="E7" s="448"/>
+      <c r="F7" s="448"/>
+      <c r="G7" s="448" t="s">
         <v>330</v>
       </c>
-      <c r="H7" s="449"/>
+      <c r="H7" s="448"/>
     </row>
     <row r="8" spans="1:19" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="482"/>
-      <c r="B8" s="482"/>
-      <c r="C8" s="482"/>
-      <c r="D8" s="482"/>
-      <c r="E8" s="482"/>
-      <c r="F8" s="482"/>
-      <c r="G8" s="482"/>
-      <c r="H8" s="482"/>
+      <c r="A8" s="474"/>
+      <c r="B8" s="474"/>
+      <c r="C8" s="474"/>
+      <c r="D8" s="474"/>
+      <c r="E8" s="474"/>
+      <c r="F8" s="474"/>
+      <c r="G8" s="474"/>
+      <c r="H8" s="474"/>
       <c r="I8" s="282"/>
       <c r="J8" s="282"/>
       <c r="K8" s="93"/>
@@ -9641,15 +9699,15 @@
       <c r="A11" s="283" t="s">
         <v>125</v>
       </c>
-      <c r="B11" s="490" t="s">
+      <c r="B11" s="489" t="s">
         <v>265</v>
       </c>
-      <c r="C11" s="491"/>
-      <c r="D11" s="491"/>
-      <c r="E11" s="491"/>
-      <c r="F11" s="491"/>
-      <c r="G11" s="491"/>
-      <c r="H11" s="492"/>
+      <c r="C11" s="490"/>
+      <c r="D11" s="490"/>
+      <c r="E11" s="490"/>
+      <c r="F11" s="490"/>
+      <c r="G11" s="490"/>
+      <c r="H11" s="491"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="284"/>
@@ -9685,15 +9743,15 @@
       <c r="A15" s="283" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="490" t="s">
+      <c r="B15" s="489" t="s">
         <v>264</v>
       </c>
-      <c r="C15" s="491"/>
-      <c r="D15" s="491"/>
-      <c r="E15" s="491"/>
-      <c r="F15" s="491"/>
-      <c r="G15" s="491"/>
-      <c r="H15" s="492"/>
+      <c r="C15" s="490"/>
+      <c r="D15" s="490"/>
+      <c r="E15" s="490"/>
+      <c r="F15" s="490"/>
+      <c r="G15" s="490"/>
+      <c r="H15" s="491"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="191"/>
@@ -9731,21 +9789,21 @@
     <row r="20" spans="1:9" s="93" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C20" s="39"/>
       <c r="D20" s="39"/>
-      <c r="F20" s="380" t="s">
+      <c r="F20" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="G20" s="380"/>
-      <c r="H20" s="380"/>
+      <c r="G20" s="372"/>
+      <c r="H20" s="372"/>
       <c r="I20" s="39"/>
     </row>
     <row r="21" spans="1:9" s="93" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="173"/>
       <c r="D21" s="158"/>
-      <c r="F21" s="448" t="s">
+      <c r="F21" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="448"/>
-      <c r="H21" s="448"/>
+      <c r="G21" s="447"/>
+      <c r="H21" s="447"/>
       <c r="I21" s="158"/>
     </row>
     <row r="22" spans="1:9" s="93" customFormat="1" x14ac:dyDescent="0.3">
@@ -9781,7 +9839,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="F11" sqref="F11"/>
       <pageMargins left="0.79" right="0.34" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="77" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -9789,7 +9847,7 @@
         <oddFooter>&amp;R&amp;P</oddFooter>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="F11" sqref="F11"/>
       <pageMargins left="0.79" right="0.34" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="77" orientation="landscape" useFirstPageNumber="1" r:id="rId2"/>
@@ -9843,12 +9901,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
       <c r="E1" s="69"/>
       <c r="F1" s="69"/>
       <c r="G1" s="69"/>
@@ -9862,12 +9920,12 @@
       <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:19" ht="41.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>346</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
       <c r="E2" s="69"/>
       <c r="F2" s="69"/>
       <c r="G2" s="69"/>
@@ -9875,20 +9933,20 @@
       <c r="I2" s="69"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="435" t="s">
+      <c r="A3" s="442" t="s">
         <v>266</v>
       </c>
-      <c r="B3" s="435"/>
-      <c r="C3" s="435"/>
-      <c r="D3" s="435"/>
+      <c r="B3" s="442"/>
+      <c r="C3" s="442"/>
+      <c r="D3" s="442"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
@@ -9906,23 +9964,23 @@
       <c r="S4" s="34"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A5" s="435"/>
-      <c r="B5" s="435"/>
-      <c r="C5" s="435"/>
-      <c r="D5" s="435"/>
+      <c r="A5" s="442"/>
+      <c r="B5" s="442"/>
+      <c r="C5" s="442"/>
+      <c r="D5" s="442"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A6" s="251"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A7" s="440" t="s">
+      <c r="A7" s="434" t="s">
         <v>344</v>
       </c>
-      <c r="B7" s="440"/>
-      <c r="C7" s="493" t="s">
+      <c r="B7" s="434"/>
+      <c r="C7" s="492" t="s">
         <v>345</v>
       </c>
-      <c r="D7" s="493"/>
+      <c r="D7" s="492"/>
       <c r="I7" s="290" t="s">
         <v>293</v>
       </c>
@@ -9999,28 +10057,28 @@
     <row r="17" spans="2:8" s="69" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:8" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B18" s="35"/>
-      <c r="C18" s="435" t="s">
+      <c r="C18" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="D18" s="435"/>
+      <c r="D18" s="442"/>
       <c r="E18" s="251"/>
       <c r="F18" s="251"/>
       <c r="H18" s="35"/>
     </row>
     <row r="19" spans="2:8" s="69" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
-      <c r="C19" s="440" t="s">
+      <c r="C19" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="D19" s="440"/>
+      <c r="D19" s="434"/>
       <c r="G19" s="56"/>
       <c r="H19" s="54"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="C20" s="429" t="s">
+      <c r="C20" s="433" t="s">
         <v>297</v>
       </c>
-      <c r="D20" s="429"/>
+      <c r="D20" s="433"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -10068,14 +10126,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="447" t="s">
         <v>139</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
       <c r="G1" s="93"/>
       <c r="H1" s="93"/>
       <c r="I1" s="93"/>
@@ -10087,39 +10145,39 @@
       <c r="O1" s="93"/>
     </row>
     <row r="2" spans="1:19" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>347</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
       <c r="G2" s="93"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93"/>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="372" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380"/>
-      <c r="F3" s="380"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
       <c r="G3" s="222"/>
       <c r="H3" s="222"/>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
       <c r="G4" s="34"/>
       <c r="H4" s="34"/>
       <c r="I4" s="34"/>
@@ -10141,16 +10199,16 @@
       <c r="B6" s="222"/>
     </row>
     <row r="7" spans="1:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="448" t="s">
+      <c r="A7" s="447" t="s">
         <v>344</v>
       </c>
-      <c r="B7" s="448"/>
-      <c r="C7" s="448"/>
-      <c r="D7" s="494" t="s">
+      <c r="B7" s="447"/>
+      <c r="C7" s="447"/>
+      <c r="D7" s="493" t="s">
         <v>345</v>
       </c>
-      <c r="E7" s="494"/>
-      <c r="F7" s="494"/>
+      <c r="E7" s="493"/>
+      <c r="F7" s="493"/>
       <c r="I7" s="321" t="s">
         <v>293</v>
       </c>
@@ -10234,18 +10292,18 @@
     </row>
     <row r="15" spans="1:19" s="93" customFormat="1" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:19" s="93" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D16" s="380" t="s">
+      <c r="D16" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="E16" s="380"/>
-      <c r="F16" s="380"/>
+      <c r="E16" s="372"/>
+      <c r="F16" s="372"/>
     </row>
     <row r="17" spans="1:19" s="93" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D17" s="448" t="s">
+      <c r="D17" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="448"/>
-      <c r="F17" s="448"/>
+      <c r="E17" s="447"/>
+      <c r="F17" s="447"/>
     </row>
     <row r="18" spans="1:19" s="93" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="451" t="s">
@@ -10263,14 +10321,14 @@
       <c r="F20" s="173"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A21" s="448" t="s">
+      <c r="A21" s="447" t="s">
         <v>200</v>
       </c>
-      <c r="B21" s="448"/>
-      <c r="C21" s="448"/>
-      <c r="D21" s="448"/>
-      <c r="E21" s="448"/>
-      <c r="F21" s="448"/>
+      <c r="B21" s="447"/>
+      <c r="C21" s="447"/>
+      <c r="D21" s="447"/>
+      <c r="E21" s="447"/>
+      <c r="F21" s="447"/>
       <c r="G21" s="93"/>
       <c r="H21" s="93"/>
       <c r="I21" s="93"/>
@@ -10282,39 +10340,39 @@
       <c r="O21" s="93"/>
     </row>
     <row r="22" spans="1:19" ht="35.549999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="448" t="s">
+      <c r="A22" s="447" t="s">
         <v>348</v>
       </c>
-      <c r="B22" s="448"/>
-      <c r="C22" s="448"/>
-      <c r="D22" s="448"/>
-      <c r="E22" s="448"/>
-      <c r="F22" s="448"/>
+      <c r="B22" s="447"/>
+      <c r="C22" s="447"/>
+      <c r="D22" s="447"/>
+      <c r="E22" s="447"/>
+      <c r="F22" s="447"/>
       <c r="G22" s="93"/>
       <c r="H22" s="93"/>
       <c r="I22" s="93"/>
     </row>
     <row r="23" spans="1:19" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="380" t="s">
+      <c r="A23" s="372" t="s">
         <v>201</v>
       </c>
-      <c r="B23" s="380"/>
-      <c r="C23" s="380"/>
-      <c r="D23" s="380"/>
-      <c r="E23" s="380"/>
-      <c r="F23" s="380"/>
+      <c r="B23" s="372"/>
+      <c r="C23" s="372"/>
+      <c r="D23" s="372"/>
+      <c r="E23" s="372"/>
+      <c r="F23" s="372"/>
       <c r="G23" s="222"/>
       <c r="H23" s="222"/>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="377" t="s">
+      <c r="A24" s="400" t="s">
         <v>222</v>
       </c>
-      <c r="B24" s="377"/>
-      <c r="C24" s="377"/>
-      <c r="D24" s="377"/>
-      <c r="E24" s="377"/>
-      <c r="F24" s="377"/>
+      <c r="B24" s="400"/>
+      <c r="C24" s="400"/>
+      <c r="D24" s="400"/>
+      <c r="E24" s="400"/>
+      <c r="F24" s="400"/>
       <c r="G24" s="34"/>
       <c r="H24" s="34"/>
       <c r="I24" s="34"/>
@@ -10346,16 +10404,16 @@
       <c r="F26" s="173"/>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A27" s="448" t="s">
+      <c r="A27" s="447" t="s">
         <v>344</v>
       </c>
-      <c r="B27" s="448"/>
-      <c r="C27" s="448"/>
-      <c r="D27" s="494" t="s">
+      <c r="B27" s="447"/>
+      <c r="C27" s="447"/>
+      <c r="D27" s="493" t="s">
         <v>345</v>
       </c>
-      <c r="E27" s="494"/>
-      <c r="F27" s="494"/>
+      <c r="E27" s="493"/>
+      <c r="F27" s="493"/>
     </row>
     <row r="28" spans="1:19" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="222"/>
@@ -10437,21 +10495,21 @@
     <row r="35" spans="1:9" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C36" s="39"/>
-      <c r="D36" s="380" t="s">
+      <c r="D36" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="E36" s="380"/>
-      <c r="F36" s="380"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
       <c r="G36" s="39"/>
       <c r="I36" s="39"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C37" s="173"/>
-      <c r="D37" s="448" t="s">
+      <c r="D37" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="E37" s="448"/>
-      <c r="F37" s="448"/>
+      <c r="E37" s="447"/>
+      <c r="F37" s="447"/>
       <c r="G37" s="173"/>
       <c r="I37" s="173"/>
     </row>
@@ -10464,7 +10522,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="A13">
+    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="A13">
       <selection activeCell="F12" sqref="F12"/>
       <pageMargins left="1.31" right="0.22" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="79" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -10472,7 +10530,7 @@
         <oddFooter>&amp;R&amp;P</oddFooter>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="A13">
+    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout" topLeftCell="A13">
       <selection activeCell="F12" sqref="F12"/>
       <pageMargins left="1.31" right="0.22" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="79" orientation="landscape" useFirstPageNumber="1" r:id="rId2"/>
@@ -10482,11 +10540,6 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="19">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A21:F21"/>
     <mergeCell ref="D37:F37"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="A27:C27"/>
@@ -10501,6 +10554,11 @@
     <mergeCell ref="A22:F22"/>
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="D27:F27"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="169" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId3"/>
@@ -10529,54 +10587,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="447" t="s">
         <v>172</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
       <c r="H1" s="93"/>
       <c r="I1" s="93"/>
     </row>
     <row r="2" spans="1:20" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>349</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
       <c r="H2" s="93"/>
       <c r="I2" s="93"/>
     </row>
     <row r="3" spans="1:20" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="372" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380"/>
-      <c r="F3" s="380"/>
-      <c r="G3" s="380"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
+      <c r="G3" s="372"/>
       <c r="H3" s="222"/>
       <c r="I3" s="222"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
       <c r="H4" s="34"/>
       <c r="I4" s="34"/>
       <c r="J4" s="34"/>
@@ -10636,16 +10694,16 @@
       <c r="T6" s="34"/>
     </row>
     <row r="7" spans="1:20" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="448" t="s">
+      <c r="A7" s="447" t="s">
         <v>350</v>
       </c>
-      <c r="B7" s="448"/>
-      <c r="C7" s="448"/>
-      <c r="E7" s="448" t="s">
+      <c r="B7" s="447"/>
+      <c r="C7" s="447"/>
+      <c r="E7" s="447" t="s">
         <v>345</v>
       </c>
-      <c r="F7" s="448"/>
-      <c r="G7" s="448"/>
+      <c r="F7" s="447"/>
+      <c r="G7" s="447"/>
       <c r="H7" s="326"/>
       <c r="I7" s="326"/>
       <c r="J7" s="326"/>
@@ -10673,25 +10731,25 @@
       <c r="T8" s="34"/>
     </row>
     <row r="9" spans="1:20" s="147" customFormat="1" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="454" t="s">
+      <c r="A9" s="453" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="452" t="s">
+      <c r="B9" s="449" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="452" t="s">
+      <c r="C9" s="449" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="452"/>
-      <c r="E9" s="452"/>
-      <c r="F9" s="452" t="s">
+      <c r="D9" s="449"/>
+      <c r="E9" s="449"/>
+      <c r="F9" s="449" t="s">
         <v>205</v>
       </c>
-      <c r="G9" s="453"/>
+      <c r="G9" s="452"/>
     </row>
     <row r="10" spans="1:20" s="147" customFormat="1" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="455"/>
-      <c r="B10" s="456"/>
+      <c r="A10" s="454"/>
+      <c r="B10" s="455"/>
       <c r="C10" s="58" t="s">
         <v>202</v>
       </c>
@@ -10789,20 +10847,20 @@
     </row>
     <row r="18" spans="1:7" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D19" s="380" t="s">
+      <c r="D19" s="372" t="s">
         <v>141</v>
       </c>
-      <c r="E19" s="380"/>
-      <c r="F19" s="380"/>
-      <c r="G19" s="380"/>
+      <c r="E19" s="372"/>
+      <c r="F19" s="372"/>
+      <c r="G19" s="372"/>
     </row>
     <row r="20" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D20" s="448" t="s">
+      <c r="D20" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="E20" s="448"/>
-      <c r="F20" s="448"/>
-      <c r="G20" s="448"/>
+      <c r="E20" s="447"/>
+      <c r="F20" s="447"/>
+      <c r="G20" s="447"/>
     </row>
     <row r="21" spans="1:7" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="451" t="s">
@@ -10854,56 +10912,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
-      <c r="E1" s="440"/>
-      <c r="F1" s="440"/>
-      <c r="G1" s="440"/>
-      <c r="H1" s="440"/>
-      <c r="I1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
+      <c r="H1" s="434"/>
+      <c r="I1" s="434"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>351</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="447"/>
+      <c r="I2" s="447"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A3" s="435" t="s">
+      <c r="A3" s="442" t="s">
         <v>201</v>
       </c>
-      <c r="B3" s="435"/>
-      <c r="C3" s="435"/>
-      <c r="D3" s="435"/>
-      <c r="E3" s="435"/>
-      <c r="F3" s="435"/>
-      <c r="G3" s="435"/>
-      <c r="H3" s="435"/>
-      <c r="I3" s="435"/>
+      <c r="B3" s="442"/>
+      <c r="C3" s="442"/>
+      <c r="D3" s="442"/>
+      <c r="E3" s="442"/>
+      <c r="F3" s="442"/>
+      <c r="G3" s="442"/>
+      <c r="H3" s="442"/>
+      <c r="I3" s="442"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>222</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
-      <c r="I4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
       <c r="J4" s="34"/>
       <c r="K4" s="34"/>
       <c r="L4" s="34"/>
@@ -10912,31 +10970,31 @@
       <c r="O4" s="34"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A5" s="429"/>
-      <c r="B5" s="429"/>
-      <c r="C5" s="429"/>
-      <c r="D5" s="429"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="429"/>
-      <c r="G5" s="429"/>
-      <c r="H5" s="429"/>
-      <c r="I5" s="429"/>
+      <c r="A5" s="433"/>
+      <c r="B5" s="433"/>
+      <c r="C5" s="433"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="433"/>
+      <c r="F5" s="433"/>
+      <c r="G5" s="433"/>
+      <c r="H5" s="433"/>
+      <c r="I5" s="433"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B6" s="251"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A7" s="448" t="s">
+      <c r="A7" s="447" t="s">
         <v>350</v>
       </c>
-      <c r="B7" s="448"/>
-      <c r="C7" s="448"/>
-      <c r="F7" s="494" t="s">
+      <c r="B7" s="447"/>
+      <c r="C7" s="447"/>
+      <c r="F7" s="493" t="s">
         <v>345</v>
       </c>
-      <c r="G7" s="494"/>
-      <c r="H7" s="494"/>
-      <c r="I7" s="494"/>
+      <c r="G7" s="493"/>
+      <c r="H7" s="493"/>
+      <c r="I7" s="493"/>
     </row>
     <row r="8" spans="1:15" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B8" s="251"/>
@@ -11072,11 +11130,11 @@
       <c r="C18" s="35"/>
       <c r="E18" s="35"/>
       <c r="F18" s="35"/>
-      <c r="G18" s="435" t="s">
+      <c r="G18" s="442" t="s">
         <v>141</v>
       </c>
-      <c r="H18" s="435"/>
-      <c r="I18" s="435"/>
+      <c r="H18" s="442"/>
+      <c r="I18" s="442"/>
       <c r="K18" s="35"/>
       <c r="L18" s="35"/>
     </row>
@@ -11084,20 +11142,20 @@
       <c r="C19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
-      <c r="G19" s="440" t="s">
+      <c r="G19" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="H19" s="440"/>
-      <c r="I19" s="440"/>
+      <c r="H19" s="434"/>
+      <c r="I19" s="434"/>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
     </row>
     <row r="20" spans="3:12" x14ac:dyDescent="0.3">
-      <c r="G20" s="429" t="s">
+      <c r="G20" s="433" t="s">
         <v>297</v>
       </c>
-      <c r="H20" s="429"/>
-      <c r="I20" s="429"/>
+      <c r="H20" s="433"/>
+      <c r="I20" s="433"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -11137,11 +11195,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>211</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
       <c r="D1" s="69"/>
       <c r="E1" s="69"/>
       <c r="F1" s="69"/>
@@ -11156,25 +11214,25 @@
       <c r="O1" s="69"/>
     </row>
     <row r="2" spans="1:15" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="396" t="s">
+      <c r="A2" s="373" t="s">
         <v>352</v>
       </c>
-      <c r="B2" s="396"/>
-      <c r="C2" s="396"/>
+      <c r="B2" s="373"/>
+      <c r="C2" s="373"/>
     </row>
     <row r="3" spans="1:15" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="372" t="s">
         <v>295</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
       <c r="D4" s="34"/>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
@@ -11193,10 +11251,10 @@
       <c r="B6" s="251"/>
     </row>
     <row r="7" spans="1:15" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="495" t="s">
+      <c r="A7" s="494" t="s">
         <v>353</v>
       </c>
-      <c r="B7" s="495"/>
+      <c r="B7" s="494"/>
       <c r="C7" s="304" t="s">
         <v>354</v>
       </c>
@@ -11287,11 +11345,11 @@
       <c r="C21" s="4"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A22" s="440" t="s">
+      <c r="A22" s="434" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="440"/>
-      <c r="C22" s="440"/>
+      <c r="B22" s="434"/>
+      <c r="C22" s="434"/>
       <c r="D22" s="69"/>
       <c r="E22" s="69"/>
       <c r="F22" s="69"/>
@@ -11306,25 +11364,25 @@
       <c r="O22" s="69"/>
     </row>
     <row r="23" spans="1:15" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="396" t="s">
+      <c r="A23" s="373" t="s">
         <v>269</v>
       </c>
-      <c r="B23" s="396"/>
-      <c r="C23" s="396"/>
+      <c r="B23" s="373"/>
+      <c r="C23" s="373"/>
     </row>
     <row r="24" spans="1:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="380" t="s">
+      <c r="A24" s="372" t="s">
         <v>268</v>
       </c>
-      <c r="B24" s="380"/>
-      <c r="C24" s="380"/>
+      <c r="B24" s="372"/>
+      <c r="C24" s="372"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="377" t="s">
+      <c r="A25" s="400" t="s">
         <v>223</v>
       </c>
-      <c r="B25" s="377"/>
-      <c r="C25" s="377"/>
+      <c r="B25" s="400"/>
+      <c r="C25" s="400"/>
       <c r="D25" s="34"/>
       <c r="E25" s="34"/>
       <c r="F25" s="34"/>
@@ -11343,10 +11401,10 @@
       <c r="B27" s="251"/>
     </row>
     <row r="28" spans="1:15" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="495" t="s">
+      <c r="A28" s="494" t="s">
         <v>210</v>
       </c>
-      <c r="B28" s="495"/>
+      <c r="B28" s="494"/>
       <c r="C28" s="304" t="s">
         <v>294</v>
       </c>
@@ -11467,16 +11525,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A28:B28"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A7:B7"/>
   </mergeCells>
   <pageMargins left="1.1811023622047245" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="172" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
@@ -11505,60 +11563,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>136</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
-      <c r="E1" s="440"/>
-      <c r="F1" s="440"/>
-      <c r="G1" s="440"/>
-      <c r="H1" s="440"/>
-      <c r="I1" s="440"/>
-      <c r="J1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
+      <c r="H1" s="434"/>
+      <c r="I1" s="434"/>
+      <c r="J1" s="434"/>
     </row>
     <row r="2" spans="1:10" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>340</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="448"/>
-      <c r="J2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="447"/>
+      <c r="I2" s="447"/>
+      <c r="J2" s="447"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A3" s="441" t="s">
+      <c r="A3" s="435" t="s">
         <v>270</v>
       </c>
-      <c r="B3" s="441"/>
-      <c r="C3" s="441"/>
-      <c r="D3" s="441"/>
-      <c r="E3" s="441"/>
-      <c r="F3" s="441"/>
-      <c r="G3" s="441"/>
-      <c r="H3" s="441"/>
-      <c r="I3" s="441"/>
-      <c r="J3" s="441"/>
+      <c r="B3" s="435"/>
+      <c r="C3" s="435"/>
+      <c r="D3" s="435"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="435"/>
+      <c r="I3" s="435"/>
+      <c r="J3" s="435"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
-      <c r="I4" s="377"/>
-      <c r="J4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
+      <c r="J4" s="400"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="251"/>
@@ -11584,32 +11642,32 @@
       <c r="B8" s="251"/>
     </row>
     <row r="9" spans="1:10" s="93" customFormat="1" ht="78" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="442" t="s">
+      <c r="A9" s="436" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="436" t="s">
+      <c r="B9" s="443" t="s">
         <v>128</v>
       </c>
-      <c r="C9" s="436" t="s">
+      <c r="C9" s="443" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="436"/>
-      <c r="E9" s="436" t="s">
+      <c r="D9" s="443"/>
+      <c r="E9" s="443" t="s">
         <v>169</v>
       </c>
-      <c r="F9" s="436"/>
-      <c r="G9" s="436" t="s">
+      <c r="F9" s="443"/>
+      <c r="G9" s="443" t="s">
         <v>170</v>
       </c>
-      <c r="H9" s="438"/>
-      <c r="I9" s="496" t="s">
+      <c r="H9" s="445"/>
+      <c r="I9" s="495" t="s">
         <v>339</v>
       </c>
-      <c r="J9" s="497"/>
+      <c r="J9" s="496"/>
     </row>
     <row r="10" spans="1:10" s="93" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="443"/>
-      <c r="B10" s="437"/>
+      <c r="A10" s="437"/>
+      <c r="B10" s="444"/>
       <c r="C10" s="40" t="s">
         <v>167</v>
       </c>
@@ -11745,12 +11803,12 @@
     <row r="19" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D19" s="69"/>
       <c r="E19" s="69"/>
-      <c r="G19" s="435" t="s">
+      <c r="G19" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="H19" s="435"/>
-      <c r="I19" s="435"/>
-      <c r="J19" s="435"/>
+      <c r="H19" s="442"/>
+      <c r="I19" s="442"/>
+      <c r="J19" s="442"/>
       <c r="K19" s="229"/>
       <c r="M19" s="229"/>
       <c r="N19" s="229"/>
@@ -11761,12 +11819,12 @@
     <row r="20" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D20" s="37"/>
       <c r="E20" s="37"/>
-      <c r="G20" s="440" t="s">
+      <c r="G20" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="H20" s="440"/>
-      <c r="I20" s="440"/>
-      <c r="J20" s="440"/>
+      <c r="H20" s="434"/>
+      <c r="I20" s="434"/>
+      <c r="J20" s="434"/>
       <c r="K20" s="229"/>
       <c r="M20" s="229"/>
       <c r="N20" s="229"/>
@@ -11777,12 +11835,12 @@
     <row r="21" spans="1:17" s="56" customFormat="1" x14ac:dyDescent="0.3">
       <c r="D21" s="37"/>
       <c r="E21" s="37"/>
-      <c r="G21" s="429" t="s">
+      <c r="G21" s="433" t="s">
         <v>297</v>
       </c>
-      <c r="H21" s="429"/>
-      <c r="I21" s="429"/>
-      <c r="J21" s="429"/>
+      <c r="H21" s="433"/>
+      <c r="I21" s="433"/>
+      <c r="J21" s="433"/>
       <c r="K21" s="229"/>
       <c r="M21" s="229"/>
       <c r="N21" s="229"/>
@@ -11834,36 +11892,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>224</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
     </row>
     <row r="2" spans="1:8" s="37" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>335</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
     </row>
     <row r="3" spans="1:8" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="372" t="s">
         <v>336</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="380"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
     </row>
     <row r="4" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
       <c r="G4" s="34"/>
@@ -11890,10 +11948,10 @@
       <c r="H6" s="34"/>
     </row>
     <row r="7" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="440" t="s">
+      <c r="A7" s="434" t="s">
         <v>271</v>
       </c>
-      <c r="B7" s="440"/>
+      <c r="B7" s="434"/>
       <c r="C7" s="178" t="s">
         <v>296</v>
       </c>
@@ -12096,10 +12154,10 @@
     <row r="29" spans="1:15" s="53" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A29" s="54"/>
       <c r="B29" s="56"/>
-      <c r="C29" s="435" t="s">
+      <c r="C29" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="D29" s="435"/>
+      <c r="D29" s="442"/>
       <c r="F29" s="55"/>
       <c r="G29" s="55"/>
       <c r="H29" s="55"/>
@@ -12113,10 +12171,10 @@
     <row r="30" spans="1:15" s="53" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A30" s="54"/>
       <c r="B30" s="56"/>
-      <c r="C30" s="440" t="s">
+      <c r="C30" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="D30" s="440"/>
+      <c r="D30" s="434"/>
       <c r="E30" s="69"/>
       <c r="F30" s="55"/>
       <c r="G30" s="55"/>
@@ -12131,10 +12189,10 @@
     <row r="31" spans="1:15" s="53" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A31" s="54"/>
       <c r="B31" s="56"/>
-      <c r="C31" s="429" t="s">
+      <c r="C31" s="433" t="s">
         <v>297</v>
       </c>
-      <c r="D31" s="429"/>
+      <c r="D31" s="433"/>
       <c r="E31" s="37"/>
       <c r="F31" s="55"/>
       <c r="G31" s="55"/>
@@ -12172,11 +12230,11 @@
     </row>
     <row r="36" spans="1:4" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="4"/>
-      <c r="B36" s="434" t="s">
+      <c r="B36" s="418" t="s">
         <v>338</v>
       </c>
-      <c r="C36" s="434"/>
-      <c r="D36" s="434"/>
+      <c r="C36" s="418"/>
+      <c r="D36" s="418"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -12213,52 +12271,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="375" t="s">
+      <c r="A1" s="398" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="375"/>
-      <c r="C1" s="375"/>
-      <c r="D1" s="375"/>
+      <c r="B1" s="398"/>
+      <c r="C1" s="398"/>
+      <c r="D1" s="398"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A2" s="375" t="s">
+      <c r="A2" s="398" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="375"/>
-      <c r="C2" s="375"/>
-      <c r="D2" s="375"/>
+      <c r="B2" s="398"/>
+      <c r="C2" s="398"/>
+      <c r="D2" s="398"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A3" s="376" t="s">
+      <c r="A3" s="399" t="s">
         <v>363</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
     </row>
     <row r="4" spans="1:25" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>303</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A5" s="377"/>
-      <c r="B5" s="377"/>
-      <c r="C5" s="377"/>
-      <c r="D5" s="377"/>
+      <c r="A5" s="400"/>
+      <c r="B5" s="400"/>
+      <c r="C5" s="400"/>
+      <c r="D5" s="400"/>
     </row>
     <row r="6" spans="1:25" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="379" t="s">
+      <c r="A6" s="375" t="s">
         <v>228</v>
       </c>
-      <c r="B6" s="379"/>
-      <c r="C6" s="410" t="s">
+      <c r="B6" s="375"/>
+      <c r="C6" s="414" t="s">
         <v>356</v>
       </c>
-      <c r="D6" s="410"/>
+      <c r="D6" s="414"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="6"/>
@@ -12267,12 +12325,12 @@
       <c r="D7" s="6"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A8" s="379" t="s">
+      <c r="A8" s="375" t="s">
         <v>144</v>
       </c>
-      <c r="B8" s="379"/>
-      <c r="C8" s="379"/>
-      <c r="D8" s="379"/>
+      <c r="B8" s="375"/>
+      <c r="C8" s="375"/>
+      <c r="D8" s="375"/>
       <c r="E8" s="33"/>
       <c r="F8" s="33"/>
       <c r="G8" s="33"/>
@@ -12299,9 +12357,9 @@
       <c r="A9" s="223" t="s">
         <v>318</v>
       </c>
-      <c r="B9" s="408"/>
-      <c r="C9" s="408"/>
-      <c r="D9" s="409"/>
+      <c r="B9" s="416"/>
+      <c r="C9" s="416"/>
+      <c r="D9" s="417"/>
       <c r="E9" s="15"/>
       <c r="F9" s="15"/>
       <c r="G9" s="15"/>
@@ -12328,18 +12386,18 @@
       <c r="A10" s="224" t="s">
         <v>317</v>
       </c>
-      <c r="B10" s="373" t="s">
+      <c r="B10" s="387" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="373"/>
+      <c r="C10" s="387"/>
       <c r="D10" s="225"/>
       <c r="E10" s="33"/>
       <c r="F10" s="33"/>
       <c r="G10" s="33"/>
-      <c r="H10" s="406"/>
-      <c r="I10" s="406"/>
-      <c r="J10" s="406"/>
-      <c r="K10" s="406"/>
+      <c r="H10" s="411"/>
+      <c r="I10" s="411"/>
+      <c r="J10" s="411"/>
+      <c r="K10" s="411"/>
       <c r="L10" s="33"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
@@ -12359,16 +12417,16 @@
       <c r="A11" s="224" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="386"/>
-      <c r="C11" s="386"/>
-      <c r="D11" s="407"/>
+      <c r="B11" s="390"/>
+      <c r="C11" s="390"/>
+      <c r="D11" s="409"/>
       <c r="E11" s="33"/>
       <c r="F11" s="33"/>
-      <c r="G11" s="405"/>
-      <c r="H11" s="405"/>
-      <c r="I11" s="406"/>
-      <c r="J11" s="406"/>
-      <c r="K11" s="406"/>
+      <c r="G11" s="415"/>
+      <c r="H11" s="415"/>
+      <c r="I11" s="411"/>
+      <c r="J11" s="411"/>
+      <c r="K11" s="411"/>
       <c r="L11" s="33"/>
       <c r="M11" s="33"/>
       <c r="N11" s="33"/>
@@ -12388,9 +12446,9 @@
       <c r="A12" s="148" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="386"/>
-      <c r="C12" s="386"/>
-      <c r="D12" s="407"/>
+      <c r="B12" s="390"/>
+      <c r="C12" s="390"/>
+      <c r="D12" s="409"/>
       <c r="E12" s="15"/>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -12417,9 +12475,9 @@
       <c r="A13" s="148" t="s">
         <v>319</v>
       </c>
-      <c r="B13" s="386"/>
-      <c r="C13" s="386"/>
-      <c r="D13" s="407"/>
+      <c r="B13" s="390"/>
+      <c r="C13" s="390"/>
+      <c r="D13" s="409"/>
       <c r="E13" s="15"/>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
@@ -12446,16 +12504,16 @@
       <c r="A14" s="224" t="s">
         <v>65</v>
       </c>
-      <c r="B14" s="386"/>
-      <c r="C14" s="386"/>
-      <c r="D14" s="407"/>
+      <c r="B14" s="390"/>
+      <c r="C14" s="390"/>
+      <c r="D14" s="409"/>
       <c r="E14" s="33"/>
       <c r="F14" s="33"/>
       <c r="G14" s="33"/>
-      <c r="H14" s="406"/>
-      <c r="I14" s="406"/>
-      <c r="J14" s="406"/>
-      <c r="K14" s="406"/>
+      <c r="H14" s="411"/>
+      <c r="I14" s="411"/>
+      <c r="J14" s="411"/>
+      <c r="K14" s="411"/>
       <c r="L14" s="33"/>
       <c r="M14" s="33"/>
       <c r="N14" s="33"/>
@@ -12475,18 +12533,18 @@
       <c r="A15" s="224" t="s">
         <v>320</v>
       </c>
-      <c r="B15" s="373" t="s">
+      <c r="B15" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="373"/>
+      <c r="C15" s="387"/>
       <c r="D15" s="226"/>
-      <c r="E15" s="411"/>
-      <c r="F15" s="406"/>
-      <c r="G15" s="406"/>
-      <c r="H15" s="406"/>
-      <c r="I15" s="406"/>
-      <c r="J15" s="406"/>
-      <c r="K15" s="406"/>
+      <c r="E15" s="412"/>
+      <c r="F15" s="411"/>
+      <c r="G15" s="411"/>
+      <c r="H15" s="411"/>
+      <c r="I15" s="411"/>
+      <c r="J15" s="411"/>
+      <c r="K15" s="411"/>
       <c r="L15" s="33"/>
       <c r="M15" s="33"/>
       <c r="N15" s="33"/>
@@ -12506,9 +12564,9 @@
       <c r="A16" s="224" t="s">
         <v>321</v>
       </c>
-      <c r="B16" s="386"/>
-      <c r="C16" s="386"/>
-      <c r="D16" s="407"/>
+      <c r="B16" s="390"/>
+      <c r="C16" s="390"/>
+      <c r="D16" s="409"/>
       <c r="E16" s="142"/>
       <c r="F16" s="15"/>
       <c r="G16" s="15"/>
@@ -12535,9 +12593,9 @@
       <c r="A17" s="224" t="s">
         <v>67</v>
       </c>
-      <c r="B17" s="386"/>
-      <c r="C17" s="386"/>
-      <c r="D17" s="407"/>
+      <c r="B17" s="390"/>
+      <c r="C17" s="390"/>
+      <c r="D17" s="409"/>
       <c r="E17" s="142"/>
       <c r="F17" s="15"/>
       <c r="G17" s="15"/>
@@ -12564,10 +12622,10 @@
       <c r="A18" s="227" t="s">
         <v>68</v>
       </c>
-      <c r="B18" s="412" t="s">
+      <c r="B18" s="413" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="412"/>
+      <c r="C18" s="413"/>
       <c r="D18" s="228"/>
     </row>
     <row r="19" spans="1:238" x14ac:dyDescent="0.3">
@@ -12577,12 +12635,12 @@
       <c r="D19" s="16"/>
     </row>
     <row r="20" spans="1:238" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="390" t="s">
+      <c r="A20" s="394" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="390"/>
-      <c r="C20" s="390"/>
-      <c r="D20" s="390"/>
+      <c r="B20" s="394"/>
+      <c r="C20" s="394"/>
+      <c r="D20" s="394"/>
       <c r="E20" s="135"/>
       <c r="F20" s="135"/>
       <c r="G20" s="135"/>
@@ -13092,7 +13150,7 @@
         <v>72</v>
       </c>
       <c r="C49" s="24"/>
-      <c r="D49" s="418" t="s">
+      <c r="D49" s="410" t="s">
         <v>83</v>
       </c>
     </row>
@@ -13104,7 +13162,7 @@
         <v>72</v>
       </c>
       <c r="C50" s="24"/>
-      <c r="D50" s="418"/>
+      <c r="D50" s="410"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="22" t="s">
@@ -13114,7 +13172,7 @@
         <v>72</v>
       </c>
       <c r="C51" s="24"/>
-      <c r="D51" s="418"/>
+      <c r="D51" s="410"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="22" t="s">
@@ -13124,7 +13182,7 @@
         <v>41</v>
       </c>
       <c r="C52" s="24"/>
-      <c r="D52" s="418"/>
+      <c r="D52" s="410"/>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="129" t="s">
@@ -13134,7 +13192,7 @@
         <v>41</v>
       </c>
       <c r="C53" s="26"/>
-      <c r="D53" s="418"/>
+      <c r="D53" s="410"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="129" t="s">
@@ -13144,7 +13202,7 @@
         <v>41</v>
       </c>
       <c r="C54" s="24"/>
-      <c r="D54" s="418"/>
+      <c r="D54" s="410"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="354" t="s">
@@ -13152,7 +13210,7 @@
       </c>
       <c r="B55" s="355"/>
       <c r="C55" s="24"/>
-      <c r="D55" s="418"/>
+      <c r="D55" s="410"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="356" t="s">
@@ -13162,7 +13220,7 @@
         <v>379</v>
       </c>
       <c r="C56" s="24"/>
-      <c r="D56" s="418"/>
+      <c r="D56" s="410"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="356" t="s">
@@ -13172,7 +13230,7 @@
         <v>382</v>
       </c>
       <c r="C57" s="24"/>
-      <c r="D57" s="418"/>
+      <c r="D57" s="410"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="356" t="s">
@@ -13182,7 +13240,7 @@
         <v>384</v>
       </c>
       <c r="C58" s="24"/>
-      <c r="D58" s="418"/>
+      <c r="D58" s="410"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="356" t="s">
@@ -13192,7 +13250,7 @@
         <v>380</v>
       </c>
       <c r="C59" s="24"/>
-      <c r="D59" s="418"/>
+      <c r="D59" s="410"/>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" s="356" t="s">
@@ -13200,7 +13258,7 @@
       </c>
       <c r="B60" s="357"/>
       <c r="C60" s="24"/>
-      <c r="D60" s="418"/>
+      <c r="D60" s="410"/>
     </row>
     <row r="61" spans="1:4" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A61" s="22" t="s">
@@ -13210,7 +13268,7 @@
         <v>72</v>
       </c>
       <c r="C61" s="24"/>
-      <c r="D61" s="418"/>
+      <c r="D61" s="410"/>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" s="22" t="s">
@@ -13220,7 +13278,7 @@
         <v>72</v>
       </c>
       <c r="C62" s="127"/>
-      <c r="D62" s="418"/>
+      <c r="D62" s="410"/>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" s="143" t="s">
@@ -13246,29 +13304,29 @@
       <c r="A65" s="145" t="s">
         <v>304</v>
       </c>
-      <c r="B65" s="413"/>
-      <c r="C65" s="413"/>
-      <c r="D65" s="414"/>
+      <c r="B65" s="404"/>
+      <c r="C65" s="404"/>
+      <c r="D65" s="405"/>
     </row>
     <row r="66" spans="1:4" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A66" s="146"/>
       <c r="B66" s="7"/>
     </row>
     <row r="67" spans="1:4" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="379" t="s">
+      <c r="A67" s="375" t="s">
         <v>145</v>
       </c>
-      <c r="B67" s="379"/>
-      <c r="C67" s="379"/>
-      <c r="D67" s="379"/>
+      <c r="B67" s="375"/>
+      <c r="C67" s="375"/>
+      <c r="D67" s="375"/>
     </row>
     <row r="68" spans="1:4" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="415" t="s">
+      <c r="A68" s="406" t="s">
         <v>146</v>
       </c>
-      <c r="B68" s="416"/>
-      <c r="C68" s="416"/>
-      <c r="D68" s="417"/>
+      <c r="B68" s="407"/>
+      <c r="C68" s="407"/>
+      <c r="D68" s="408"/>
     </row>
     <row r="69" spans="1:4" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A69" s="135"/>
@@ -13282,46 +13340,46 @@
       </c>
     </row>
     <row r="71" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="395" t="s">
+      <c r="A71" s="371" t="s">
         <v>106</v>
       </c>
-      <c r="B71" s="400"/>
-      <c r="C71" s="400"/>
-      <c r="D71" s="400"/>
+      <c r="B71" s="379"/>
+      <c r="C71" s="379"/>
+      <c r="D71" s="379"/>
     </row>
     <row r="72" spans="1:4" ht="51" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="401" t="s">
+      <c r="A72" s="380" t="s">
         <v>81</v>
       </c>
-      <c r="B72" s="401"/>
-      <c r="C72" s="401"/>
-      <c r="D72" s="401"/>
+      <c r="B72" s="380"/>
+      <c r="C72" s="380"/>
+      <c r="D72" s="380"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A73" s="395" t="s">
+      <c r="A73" s="371" t="s">
         <v>82</v>
       </c>
-      <c r="B73" s="395"/>
-      <c r="C73" s="395"/>
-      <c r="D73" s="395"/>
+      <c r="B73" s="371"/>
+      <c r="C73" s="371"/>
+      <c r="D73" s="371"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B75" s="380" t="s">
+      <c r="B75" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="C75" s="380"/>
-      <c r="D75" s="380"/>
+      <c r="C75" s="372"/>
+      <c r="D75" s="372"/>
     </row>
     <row r="76" spans="1:4" ht="63" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="396" t="s">
+      <c r="B76" s="373" t="s">
         <v>289</v>
       </c>
-      <c r="C76" s="396"/>
-      <c r="D76" s="396"/>
+      <c r="C76" s="373"/>
+      <c r="D76" s="373"/>
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="D47" sqref="D47"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="95" firstPageNumber="65" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
@@ -13330,7 +13388,7 @@
         <oddFooter>&amp;R&amp;P</oddFooter>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="D47" sqref="D47"/>
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" scale="95" firstPageNumber="65" orientation="portrait" useFirstPageNumber="1" r:id="rId2"/>
@@ -13341,22 +13399,12 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="34">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B65:D65"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="D49:D62"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:K11"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="H10:K10"/>
+    <mergeCell ref="B11:D11"/>
     <mergeCell ref="B75:D75"/>
     <mergeCell ref="B76:D76"/>
     <mergeCell ref="A73:D73"/>
@@ -13369,12 +13417,22 @@
     <mergeCell ref="A72:D72"/>
     <mergeCell ref="C6:D6"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:K11"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="H10:K10"/>
-    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B65:D65"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="D49:D62"/>
+    <mergeCell ref="A20:D20"/>
   </mergeCells>
   <pageMargins left="0.98425196850393704" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="155" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId3"/>
@@ -13390,640 +13448,620 @@
   <dimension ref="A1:E95"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="64.19921875" style="371" customWidth="1"/>
+    <col min="1" max="1" width="64.19921875" style="370" customWidth="1"/>
     <col min="2" max="3" width="6.796875" customWidth="1"/>
     <col min="4" max="4" width="8.19921875" customWidth="1"/>
     <col min="5" max="5" width="6.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="424" t="s">
+      <c r="A1" s="428" t="s">
         <v>390</v>
       </c>
-      <c r="B1" s="424"/>
-      <c r="C1" s="424"/>
-      <c r="D1" s="424"/>
-      <c r="E1" s="424"/>
+      <c r="B1" s="428"/>
+      <c r="C1" s="428"/>
+      <c r="D1" s="428"/>
+      <c r="E1" s="428"/>
     </row>
     <row r="2" spans="1:5" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="425" t="s">
+      <c r="A2" s="429" t="s">
         <v>391</v>
       </c>
-      <c r="B2" s="426"/>
-      <c r="C2" s="426"/>
-      <c r="D2" s="426"/>
-      <c r="E2" s="426"/>
+      <c r="B2" s="430"/>
+      <c r="C2" s="430"/>
+      <c r="D2" s="430"/>
+      <c r="E2" s="430"/>
     </row>
     <row r="3" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="427" t="s">
+      <c r="A3" s="431" t="s">
         <v>392</v>
       </c>
-      <c r="B3" s="427"/>
-      <c r="C3" s="427"/>
-      <c r="D3" s="427"/>
-      <c r="E3" s="427"/>
+      <c r="B3" s="431"/>
+      <c r="C3" s="431"/>
+      <c r="D3" s="431"/>
+      <c r="E3" s="431"/>
     </row>
     <row r="5" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="428" t="s">
+      <c r="A5" s="432" t="s">
         <v>393</v>
       </c>
-      <c r="B5" s="428"/>
-      <c r="C5" s="428"/>
-      <c r="D5" s="428"/>
-      <c r="E5" s="428"/>
+      <c r="B5" s="432"/>
+      <c r="C5" s="432"/>
+      <c r="D5" s="432"/>
+      <c r="E5" s="432"/>
     </row>
     <row r="6" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="428" t="s">
+      <c r="A6" s="432" t="s">
         <v>394</v>
       </c>
-      <c r="B6" s="428"/>
-      <c r="C6" s="428"/>
-      <c r="D6" s="428"/>
-      <c r="E6" s="428"/>
+      <c r="B6" s="432"/>
+      <c r="C6" s="432"/>
+      <c r="D6" s="432"/>
+      <c r="E6" s="432"/>
     </row>
     <row r="7" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A7" s="4"/>
     </row>
     <row r="8" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="428" t="s">
+      <c r="A8" s="432" t="s">
         <v>395</v>
       </c>
-      <c r="B8" s="428"/>
-      <c r="C8" s="428"/>
-      <c r="D8" s="428"/>
-      <c r="E8" s="428"/>
+      <c r="B8" s="432"/>
+      <c r="C8" s="432"/>
+      <c r="D8" s="432"/>
+      <c r="E8" s="432"/>
     </row>
     <row r="9" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A9" s="429" t="s">
-        <v>396</v>
-      </c>
-      <c r="B9" s="429"/>
-      <c r="C9" s="429"/>
-      <c r="D9" s="429"/>
-      <c r="E9" s="429"/>
+      <c r="A9" s="433" t="s">
+        <v>470</v>
+      </c>
+      <c r="B9" s="433"/>
+      <c r="C9" s="433"/>
+      <c r="D9" s="433"/>
+      <c r="E9" s="433"/>
     </row>
     <row r="10" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A10" s="363"/>
     </row>
     <row r="11" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A11" s="363" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>398</v>
+        <v>471</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>399</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>400</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
-        <v>401</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A16" s="364" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="67.2" x14ac:dyDescent="0.3">
       <c r="A17" s="364" t="s">
-        <v>402</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A18" s="364" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="419" t="s">
+      <c r="A19" s="423" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="419" t="s">
+      <c r="B19" s="423" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="419" t="s">
-        <v>404</v>
-      </c>
-      <c r="D19" s="419"/>
-      <c r="E19" s="419" t="s">
-        <v>405</v>
+      <c r="C19" s="423" t="s">
+        <v>398</v>
+      </c>
+      <c r="D19" s="423"/>
+      <c r="E19" s="423" t="s">
+        <v>399</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="419"/>
-      <c r="B20" s="419"/>
-      <c r="C20" s="365" t="s">
-        <v>406</v>
-      </c>
-      <c r="D20" s="365" t="s">
-        <v>407</v>
-      </c>
-      <c r="E20" s="419"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>478</v>
-      </c>
-      <c r="B21" t="s">
-        <v>479</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="A20" s="423"/>
+      <c r="B20" s="423"/>
+      <c r="C20" s="505" t="s">
+        <v>400</v>
+      </c>
+      <c r="D20" s="505" t="s">
+        <v>401</v>
+      </c>
+      <c r="E20" s="423"/>
+    </row>
+    <row r="21" spans="1:5" s="498" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="499" t="s">
         <v>480</v>
       </c>
-      <c r="D21" t="s">
+      <c r="B21" s="500" t="s">
         <v>481</v>
       </c>
-      <c r="E21" t="s">
+      <c r="C21" s="506" t="s">
         <v>482</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="365"/>
-      <c r="B22" s="365"/>
-      <c r="C22" s="365"/>
-      <c r="D22" s="365"/>
-      <c r="E22" s="365"/>
+      <c r="D21" s="506" t="s">
+        <v>483</v>
+      </c>
+      <c r="E21" s="500" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" s="498" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A22" s="497"/>
+      <c r="B22" s="497"/>
+      <c r="C22" s="497"/>
+      <c r="D22" s="497"/>
+      <c r="E22" s="497"/>
     </row>
     <row r="23" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A23" s="37" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="423" t="s">
+        <v>403</v>
+      </c>
+      <c r="B24" s="424" t="s">
+        <v>404</v>
+      </c>
+      <c r="C24" s="425"/>
+      <c r="D24" s="423" t="s">
+        <v>405</v>
+      </c>
+      <c r="E24" s="423"/>
+    </row>
+    <row r="25" spans="1:5" ht="79.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="423"/>
+      <c r="B25" s="426"/>
+      <c r="C25" s="427"/>
+      <c r="D25" s="423"/>
+      <c r="E25" s="423"/>
+    </row>
+    <row r="26" spans="1:5" s="504" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A26" s="501" t="s">
+        <v>477</v>
+      </c>
+      <c r="B26" s="502" t="s">
+        <v>479</v>
+      </c>
+      <c r="C26" s="503"/>
+      <c r="D26" s="502" t="s">
+        <v>478</v>
+      </c>
+      <c r="E26" s="503"/>
+    </row>
+    <row r="27" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A27" s="365"/>
+      <c r="B27" s="420"/>
+      <c r="C27" s="421"/>
+      <c r="D27" s="420"/>
+      <c r="E27" s="421"/>
+    </row>
+    <row r="28" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A28" s="366" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="366" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="366" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="A31" s="367" t="s">
         <v>408</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="49.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="419" t="s">
-        <v>409</v>
-      </c>
-      <c r="B24" s="420" t="s">
-        <v>410</v>
-      </c>
-      <c r="C24" s="421"/>
-      <c r="D24" s="419" t="s">
-        <v>411</v>
-      </c>
-      <c r="E24" s="419"/>
-    </row>
-    <row r="25" spans="1:5" ht="79.8" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="419"/>
-      <c r="B25" s="422"/>
-      <c r="C25" s="423"/>
-      <c r="D25" s="419"/>
-      <c r="E25" s="419"/>
-    </row>
-    <row r="26" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A26" s="366" t="s">
-        <v>484</v>
-      </c>
-      <c r="B26" s="431" t="s">
-        <v>485</v>
-      </c>
-      <c r="C26" s="432"/>
-      <c r="D26" s="431" t="s">
-        <v>486</v>
-      </c>
-      <c r="E26" s="432"/>
-    </row>
-    <row r="27" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A27" s="366"/>
-      <c r="B27" s="431"/>
-      <c r="C27" s="432"/>
-      <c r="D27" s="431"/>
-      <c r="E27" s="432"/>
-    </row>
-    <row r="28" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A28" s="367" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="367" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A30" s="367" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A31" s="368" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A32" s="364" t="s">
-        <v>415</v>
+        <v>485</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37" t="s">
-        <v>416</v>
+        <v>409</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37" t="s">
-        <v>417</v>
+        <v>410</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A36" s="364" t="s">
-        <v>418</v>
+        <v>411</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A37" s="363" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A38" s="364" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A39" s="433" t="s">
-        <v>421</v>
-      </c>
-      <c r="B39" s="433"/>
-      <c r="C39" s="433"/>
-      <c r="D39" s="433"/>
-      <c r="E39" s="433"/>
+      <c r="A39" s="422" t="s">
+        <v>414</v>
+      </c>
+      <c r="B39" s="422"/>
+      <c r="C39" s="422"/>
+      <c r="D39" s="422"/>
+      <c r="E39" s="422"/>
     </row>
     <row r="40" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A40" s="364" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A41" s="364" t="s">
-        <v>423</v>
+        <v>416</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A42" s="364" t="s">
-        <v>424</v>
+        <v>417</v>
       </c>
     </row>
     <row r="43" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A43" s="364" t="s">
-        <v>425</v>
+        <v>418</v>
       </c>
     </row>
     <row r="44" spans="1:5" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="430" t="s">
-        <v>426</v>
-      </c>
-      <c r="B44" s="430"/>
-      <c r="C44" s="430"/>
-      <c r="D44" s="430"/>
-      <c r="E44" s="430"/>
+      <c r="A44" s="419" t="s">
+        <v>419</v>
+      </c>
+      <c r="B44" s="419"/>
+      <c r="C44" s="419"/>
+      <c r="D44" s="419"/>
+      <c r="E44" s="419"/>
     </row>
     <row r="45" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A45" s="364" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A46" s="364" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="434" t="s">
-        <v>429</v>
-      </c>
-      <c r="B47" s="434"/>
-      <c r="C47" s="434"/>
-      <c r="D47" s="434"/>
-      <c r="E47" s="434"/>
+      <c r="A47" s="418" t="s">
+        <v>422</v>
+      </c>
+      <c r="B47" s="418"/>
+      <c r="C47" s="418"/>
+      <c r="D47" s="418"/>
+      <c r="E47" s="418"/>
     </row>
     <row r="48" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A48" s="434" t="s">
-        <v>430</v>
-      </c>
-      <c r="B48" s="434"/>
-      <c r="C48" s="434"/>
-      <c r="D48" s="434"/>
-      <c r="E48" s="434"/>
+      <c r="A48" s="418" t="s">
+        <v>423</v>
+      </c>
+      <c r="B48" s="418"/>
+      <c r="C48" s="418"/>
+      <c r="D48" s="418"/>
+      <c r="E48" s="418"/>
     </row>
     <row r="49" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="430" t="s">
-        <v>431</v>
-      </c>
-      <c r="B49" s="430"/>
-      <c r="C49" s="430"/>
-      <c r="D49" s="430"/>
-      <c r="E49" s="430"/>
+      <c r="A49" s="419" t="s">
+        <v>424</v>
+      </c>
+      <c r="B49" s="419"/>
+      <c r="C49" s="419"/>
+      <c r="D49" s="419"/>
+      <c r="E49" s="419"/>
     </row>
     <row r="50" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A50" s="364" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="19.2" x14ac:dyDescent="0.3">
       <c r="A51" s="364" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A52" s="364" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A53" s="364" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A54" s="364" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A55" s="364" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="43.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="434" t="s">
-        <v>438</v>
-      </c>
-      <c r="B56" s="434"/>
-      <c r="C56" s="434"/>
-      <c r="D56" s="434"/>
-      <c r="E56" s="434"/>
+      <c r="A56" s="418" t="s">
+        <v>431</v>
+      </c>
+      <c r="B56" s="418"/>
+      <c r="C56" s="418"/>
+      <c r="D56" s="418"/>
+      <c r="E56" s="418"/>
     </row>
     <row r="57" spans="1:5" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="434" t="s">
-        <v>439</v>
-      </c>
-      <c r="B57" s="434"/>
-      <c r="C57" s="434"/>
-      <c r="D57" s="434"/>
-      <c r="E57" s="434"/>
+      <c r="A57" s="418" t="s">
+        <v>432</v>
+      </c>
+      <c r="B57" s="418"/>
+      <c r="C57" s="418"/>
+      <c r="D57" s="418"/>
+      <c r="E57" s="418"/>
     </row>
     <row r="58" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A58" s="364" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="64.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="430" t="s">
-        <v>441</v>
-      </c>
-      <c r="B59" s="430"/>
-      <c r="C59" s="430"/>
-      <c r="D59" s="430"/>
-      <c r="E59" s="430"/>
+      <c r="A59" s="419" t="s">
+        <v>434</v>
+      </c>
+      <c r="B59" s="419"/>
+      <c r="C59" s="419"/>
+      <c r="D59" s="419"/>
+      <c r="E59" s="419"/>
     </row>
     <row r="60" spans="1:5" ht="36" x14ac:dyDescent="0.3">
       <c r="A60" s="364" t="s">
-        <v>442</v>
+        <v>435</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="47.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="434" t="s">
-        <v>443</v>
-      </c>
-      <c r="B61" s="434"/>
-      <c r="C61" s="434"/>
-      <c r="D61" s="434"/>
-      <c r="E61" s="434"/>
+      <c r="A61" s="418" t="s">
+        <v>436</v>
+      </c>
+      <c r="B61" s="418"/>
+      <c r="C61" s="418"/>
+      <c r="D61" s="418"/>
+      <c r="E61" s="418"/>
     </row>
     <row r="62" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A62" s="364" t="s">
-        <v>444</v>
+        <v>437</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="434" t="s">
-        <v>445</v>
-      </c>
-      <c r="B63" s="434"/>
-      <c r="C63" s="434"/>
-      <c r="D63" s="434"/>
-      <c r="E63" s="434"/>
+      <c r="A63" s="418" t="s">
+        <v>438</v>
+      </c>
+      <c r="B63" s="418"/>
+      <c r="C63" s="418"/>
+      <c r="D63" s="418"/>
+      <c r="E63" s="418"/>
     </row>
     <row r="64" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A64" s="364" t="s">
-        <v>446</v>
+        <v>439</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="434" t="s">
-        <v>447</v>
-      </c>
-      <c r="B65" s="434"/>
-      <c r="C65" s="434"/>
-      <c r="D65" s="434"/>
-      <c r="E65" s="434"/>
+      <c r="A65" s="418" t="s">
+        <v>440</v>
+      </c>
+      <c r="B65" s="418"/>
+      <c r="C65" s="418"/>
+      <c r="D65" s="418"/>
+      <c r="E65" s="418"/>
     </row>
     <row r="66" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A66" s="364" t="s">
-        <v>448</v>
+        <v>441</v>
       </c>
     </row>
     <row r="67" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A67" s="364" t="s">
-        <v>449</v>
+        <v>442</v>
       </c>
     </row>
     <row r="68" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A68" s="364" t="s">
-        <v>450</v>
+        <v>443</v>
       </c>
     </row>
     <row r="69" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A69" s="364" t="s">
-        <v>451</v>
+        <v>444</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A70" s="364" t="s">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A71" s="364" t="s">
-        <v>453</v>
+        <v>446</v>
       </c>
     </row>
     <row r="72" spans="1:5" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="434" t="s">
-        <v>454</v>
-      </c>
-      <c r="B72" s="434"/>
-      <c r="C72" s="434"/>
-      <c r="D72" s="434"/>
-      <c r="E72" s="434"/>
+      <c r="A72" s="418" t="s">
+        <v>447</v>
+      </c>
+      <c r="B72" s="418"/>
+      <c r="C72" s="418"/>
+      <c r="D72" s="418"/>
+      <c r="E72" s="418"/>
     </row>
     <row r="73" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A73" s="434" t="s">
-        <v>455</v>
-      </c>
-      <c r="B73" s="434"/>
-      <c r="C73" s="434"/>
-      <c r="D73" s="434"/>
-      <c r="E73" s="434"/>
+      <c r="A73" s="418" t="s">
+        <v>448</v>
+      </c>
+      <c r="B73" s="418"/>
+      <c r="C73" s="418"/>
+      <c r="D73" s="418"/>
+      <c r="E73" s="418"/>
     </row>
     <row r="74" spans="1:5" ht="36.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="430" t="s">
-        <v>456</v>
-      </c>
-      <c r="B74" s="430"/>
-      <c r="C74" s="430"/>
-      <c r="D74" s="430"/>
-      <c r="E74" s="430"/>
+      <c r="A74" s="419" t="s">
+        <v>449</v>
+      </c>
+      <c r="B74" s="419"/>
+      <c r="C74" s="419"/>
+      <c r="D74" s="419"/>
+      <c r="E74" s="419"/>
     </row>
     <row r="75" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A75" s="364" t="s">
-        <v>457</v>
+        <v>450</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A76" s="364" t="s">
-        <v>458</v>
+        <v>451</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A77" s="364" t="s">
-        <v>459</v>
+        <v>452</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A78" s="364" t="s">
-        <v>460</v>
+        <v>453</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A79" s="364" t="s">
-        <v>461</v>
+        <v>454</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A80" s="364" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A81" s="364" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
     </row>
     <row r="82" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A82" s="364" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A83" s="364" t="s">
-        <v>465</v>
+        <v>458</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A84" s="364" t="s">
-        <v>466</v>
+        <v>459</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="42.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="434" t="s">
-        <v>467</v>
-      </c>
-      <c r="B85" s="434"/>
-      <c r="C85" s="434"/>
-      <c r="D85" s="434"/>
-      <c r="E85" s="434"/>
+      <c r="A85" s="418" t="s">
+        <v>460</v>
+      </c>
+      <c r="B85" s="418"/>
+      <c r="C85" s="418"/>
+      <c r="D85" s="418"/>
+      <c r="E85" s="418"/>
     </row>
     <row r="86" spans="1:5" ht="33.6" x14ac:dyDescent="0.3">
       <c r="A86" s="364" t="s">
-        <v>468</v>
+        <v>461</v>
       </c>
     </row>
     <row r="87" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A87" s="37" t="s">
-        <v>469</v>
+        <v>462</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A88" s="37" t="s">
-        <v>470</v>
+        <v>463</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A89" s="363" t="s">
-        <v>471</v>
+        <v>464</v>
       </c>
     </row>
     <row r="90" spans="1:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="434" t="s">
-        <v>472</v>
-      </c>
-      <c r="B90" s="434"/>
-      <c r="C90" s="434"/>
-      <c r="D90" s="434"/>
-      <c r="E90" s="434"/>
+      <c r="A90" s="418" t="s">
+        <v>465</v>
+      </c>
+      <c r="B90" s="418"/>
+      <c r="C90" s="418"/>
+      <c r="D90" s="418"/>
+      <c r="E90" s="418"/>
     </row>
     <row r="91" spans="1:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A91" s="364" t="s">
-        <v>473</v>
+        <v>466</v>
       </c>
     </row>
     <row r="92" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="37"/>
     </row>
     <row r="93" spans="1:5" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="369" t="s">
-        <v>474</v>
+      <c r="A93" s="368" t="s">
+        <v>467</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="370" t="s">
-        <v>475</v>
+      <c r="A94" s="369" t="s">
+        <v>468</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="369" t="s">
-        <v>476</v>
+      <c r="A95" s="368" t="s">
+        <v>469</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A90:E90"/>
-    <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A65:E65"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A73:E73"/>
-    <mergeCell ref="A74:E74"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="A44:E44"/>
-    <mergeCell ref="A47:E47"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A49:E49"/>
-    <mergeCell ref="A56:E56"/>
-    <mergeCell ref="A57:E57"/>
     <mergeCell ref="A24:A25"/>
     <mergeCell ref="B24:C25"/>
     <mergeCell ref="D24:E25"/>
@@ -14038,6 +14076,26 @@
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="E19:E20"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="A39:E39"/>
+    <mergeCell ref="A44:E44"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A48:E48"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A56:E56"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A90:E90"/>
+    <mergeCell ref="A61:E61"/>
+    <mergeCell ref="A63:E63"/>
+    <mergeCell ref="A65:E65"/>
+    <mergeCell ref="A72:E72"/>
+    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A74:E74"/>
   </mergeCells>
   <pageMargins left="0.45" right="0.2" top="0.25" bottom="0.25" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -14069,102 +14127,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
-      <c r="E1" s="440"/>
-      <c r="F1" s="440"/>
-      <c r="G1" s="440"/>
-      <c r="H1" s="440"/>
-      <c r="I1" s="440"/>
-      <c r="J1" s="440"/>
-      <c r="K1" s="440"/>
-      <c r="L1" s="440"/>
-      <c r="M1" s="440"/>
-      <c r="N1" s="440"/>
-      <c r="O1" s="440"/>
-      <c r="P1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
+      <c r="H1" s="434"/>
+      <c r="I1" s="434"/>
+      <c r="J1" s="434"/>
+      <c r="K1" s="434"/>
+      <c r="L1" s="434"/>
+      <c r="M1" s="434"/>
+      <c r="N1" s="434"/>
+      <c r="O1" s="434"/>
+      <c r="P1" s="434"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="440" t="s">
+      <c r="A2" s="434" t="s">
         <v>307</v>
       </c>
-      <c r="B2" s="440"/>
-      <c r="C2" s="440"/>
-      <c r="D2" s="440"/>
-      <c r="E2" s="440"/>
-      <c r="F2" s="440"/>
-      <c r="G2" s="440"/>
-      <c r="H2" s="440"/>
-      <c r="I2" s="440"/>
-      <c r="J2" s="440"/>
-      <c r="K2" s="440"/>
-      <c r="L2" s="440"/>
-      <c r="M2" s="440"/>
-      <c r="N2" s="440"/>
-      <c r="O2" s="440"/>
-      <c r="P2" s="440"/>
+      <c r="B2" s="434"/>
+      <c r="C2" s="434"/>
+      <c r="D2" s="434"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="434"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="434"/>
+      <c r="I2" s="434"/>
+      <c r="J2" s="434"/>
+      <c r="K2" s="434"/>
+      <c r="L2" s="434"/>
+      <c r="M2" s="434"/>
+      <c r="N2" s="434"/>
+      <c r="O2" s="434"/>
+      <c r="P2" s="434"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="441" t="s">
+      <c r="A3" s="435" t="s">
         <v>362</v>
       </c>
-      <c r="B3" s="441"/>
-      <c r="C3" s="441"/>
-      <c r="D3" s="441"/>
-      <c r="E3" s="441"/>
-      <c r="F3" s="441"/>
-      <c r="G3" s="441"/>
-      <c r="H3" s="441"/>
-      <c r="I3" s="441"/>
-      <c r="J3" s="441"/>
-      <c r="K3" s="441"/>
-      <c r="L3" s="441"/>
-      <c r="M3" s="441"/>
-      <c r="N3" s="441"/>
-      <c r="O3" s="441"/>
-      <c r="P3" s="441"/>
+      <c r="B3" s="435"/>
+      <c r="C3" s="435"/>
+      <c r="D3" s="435"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="435"/>
+      <c r="I3" s="435"/>
+      <c r="J3" s="435"/>
+      <c r="K3" s="435"/>
+      <c r="L3" s="435"/>
+      <c r="M3" s="435"/>
+      <c r="N3" s="435"/>
+      <c r="O3" s="435"/>
+      <c r="P3" s="435"/>
     </row>
     <row r="4" spans="1:17" s="330" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>225</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
-      <c r="I4" s="377"/>
-      <c r="J4" s="377"/>
-      <c r="K4" s="377"/>
-      <c r="L4" s="377"/>
-      <c r="M4" s="377"/>
-      <c r="N4" s="377"/>
-      <c r="O4" s="377"/>
-      <c r="P4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
+      <c r="J4" s="400"/>
+      <c r="K4" s="400"/>
+      <c r="L4" s="400"/>
+      <c r="M4" s="400"/>
+      <c r="N4" s="400"/>
+      <c r="O4" s="400"/>
+      <c r="P4" s="400"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="435"/>
-      <c r="B5" s="435"/>
-      <c r="C5" s="435"/>
-      <c r="D5" s="435"/>
-      <c r="E5" s="435"/>
-      <c r="F5" s="435"/>
-      <c r="G5" s="435"/>
-      <c r="H5" s="435"/>
-      <c r="I5" s="435"/>
-      <c r="J5" s="435"/>
-      <c r="K5" s="435"/>
-      <c r="L5" s="435"/>
-      <c r="M5" s="435"/>
-      <c r="N5" s="435"/>
-      <c r="O5" s="435"/>
-      <c r="P5" s="435"/>
+      <c r="A5" s="442"/>
+      <c r="B5" s="442"/>
+      <c r="C5" s="442"/>
+      <c r="D5" s="442"/>
+      <c r="E5" s="442"/>
+      <c r="F5" s="442"/>
+      <c r="G5" s="442"/>
+      <c r="H5" s="442"/>
+      <c r="I5" s="442"/>
+      <c r="J5" s="442"/>
+      <c r="K5" s="442"/>
+      <c r="L5" s="442"/>
+      <c r="M5" s="442"/>
+      <c r="N5" s="442"/>
+      <c r="O5" s="442"/>
+      <c r="P5" s="442"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
@@ -14185,26 +14243,26 @@
       <c r="P6" s="3"/>
     </row>
     <row r="7" spans="1:17" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="447" t="s">
+      <c r="A7" s="441" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="447"/>
-      <c r="C7" s="447"/>
-      <c r="D7" s="447"/>
-      <c r="E7" s="447"/>
-      <c r="F7" s="447"/>
-      <c r="G7" s="447"/>
-      <c r="H7" s="447"/>
-      <c r="I7" s="447"/>
-      <c r="J7" s="447"/>
-      <c r="K7" s="447"/>
-      <c r="L7" s="446" t="s">
+      <c r="B7" s="441"/>
+      <c r="C7" s="441"/>
+      <c r="D7" s="441"/>
+      <c r="E7" s="441"/>
+      <c r="F7" s="441"/>
+      <c r="G7" s="441"/>
+      <c r="H7" s="441"/>
+      <c r="I7" s="441"/>
+      <c r="J7" s="441"/>
+      <c r="K7" s="441"/>
+      <c r="L7" s="440" t="s">
         <v>358</v>
       </c>
-      <c r="M7" s="446"/>
-      <c r="N7" s="446"/>
-      <c r="O7" s="446"/>
-      <c r="P7" s="446"/>
+      <c r="M7" s="440"/>
+      <c r="N7" s="440"/>
+      <c r="O7" s="440"/>
+      <c r="P7" s="440"/>
       <c r="Q7" s="326"/>
     </row>
     <row r="8" spans="1:17" ht="15.45" customHeight="1" x14ac:dyDescent="0.3">
@@ -14224,76 +14282,76 @@
       </c>
     </row>
     <row r="10" spans="1:17" s="39" customFormat="1" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="442" t="s">
+      <c r="A10" s="436" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="436" t="s">
+      <c r="B10" s="443" t="s">
         <v>58</v>
       </c>
-      <c r="C10" s="436" t="s">
+      <c r="C10" s="443" t="s">
         <v>1</v>
       </c>
-      <c r="D10" s="436" t="s">
+      <c r="D10" s="443" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="444" t="s">
+      <c r="E10" s="438" t="s">
         <v>50</v>
       </c>
-      <c r="F10" s="436" t="s">
+      <c r="F10" s="443" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="436" t="s">
+      <c r="G10" s="443" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="436" t="s">
+      <c r="H10" s="443" t="s">
         <v>25</v>
       </c>
-      <c r="I10" s="436"/>
-      <c r="J10" s="436" t="s">
+      <c r="I10" s="443"/>
+      <c r="J10" s="443" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="436" t="s">
+      <c r="K10" s="443" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="436" t="s">
+      <c r="L10" s="443" t="s">
         <v>29</v>
       </c>
-      <c r="M10" s="436" t="s">
+      <c r="M10" s="443" t="s">
         <v>31</v>
       </c>
-      <c r="N10" s="436" t="s">
+      <c r="N10" s="443" t="s">
         <v>16</v>
       </c>
-      <c r="O10" s="436"/>
-      <c r="P10" s="438" t="s">
+      <c r="O10" s="443"/>
+      <c r="P10" s="445" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="39" customFormat="1" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="443"/>
-      <c r="B11" s="437"/>
-      <c r="C11" s="437"/>
-      <c r="D11" s="437"/>
-      <c r="E11" s="445"/>
-      <c r="F11" s="437"/>
-      <c r="G11" s="437"/>
+      <c r="A11" s="437"/>
+      <c r="B11" s="444"/>
+      <c r="C11" s="444"/>
+      <c r="D11" s="444"/>
+      <c r="E11" s="439"/>
+      <c r="F11" s="444"/>
+      <c r="G11" s="444"/>
       <c r="H11" s="41" t="s">
         <v>311</v>
       </c>
       <c r="I11" s="41" t="s">
         <v>312</v>
       </c>
-      <c r="J11" s="437"/>
-      <c r="K11" s="437"/>
-      <c r="L11" s="437"/>
-      <c r="M11" s="437"/>
+      <c r="J11" s="444"/>
+      <c r="K11" s="444"/>
+      <c r="L11" s="444"/>
+      <c r="M11" s="444"/>
       <c r="N11" s="40" t="s">
         <v>309</v>
       </c>
       <c r="O11" s="40" t="s">
         <v>310</v>
       </c>
-      <c r="P11" s="439"/>
+      <c r="P11" s="446"/>
     </row>
     <row r="12" spans="1:17" s="45" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="42">
@@ -14578,32 +14636,24 @@
       <c r="E26" s="4"/>
       <c r="G26" s="4"/>
       <c r="L26" s="336"/>
-      <c r="M26" s="435" t="s">
+      <c r="M26" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="N26" s="435"/>
-      <c r="O26" s="435"/>
-      <c r="P26" s="435"/>
+      <c r="N26" s="442"/>
+      <c r="O26" s="442"/>
+      <c r="P26" s="442"/>
     </row>
     <row r="27" spans="1:16" ht="50.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="L27" s="396" t="s">
+      <c r="L27" s="373" t="s">
         <v>298</v>
       </c>
-      <c r="M27" s="396"/>
-      <c r="N27" s="396"/>
-      <c r="O27" s="396"/>
-      <c r="P27" s="396"/>
+      <c r="M27" s="373"/>
+      <c r="N27" s="373"/>
+      <c r="O27" s="373"/>
+      <c r="P27" s="373"/>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A4:P4"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="L7:P7"/>
-    <mergeCell ref="A7:K7"/>
     <mergeCell ref="L27:P27"/>
     <mergeCell ref="A5:P5"/>
     <mergeCell ref="F10:F11"/>
@@ -14619,6 +14669,14 @@
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="D10:D11"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A3:P3"/>
+    <mergeCell ref="A4:P4"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="L7:P7"/>
+    <mergeCell ref="A7:K7"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="87" firstPageNumber="157" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -14644,48 +14702,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="140" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="447" t="s">
         <v>364</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
       <c r="G1" s="175"/>
       <c r="H1" s="175"/>
       <c r="I1" s="175"/>
       <c r="J1" s="175"/>
     </row>
     <row r="2" spans="1:16" s="176" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="375" t="s">
+      <c r="A2" s="398" t="s">
         <v>308</v>
       </c>
-      <c r="B2" s="375"/>
-      <c r="C2" s="375"/>
-      <c r="D2" s="375"/>
-      <c r="E2" s="375"/>
-      <c r="F2" s="375"/>
+      <c r="B2" s="398"/>
+      <c r="C2" s="398"/>
+      <c r="D2" s="398"/>
+      <c r="E2" s="398"/>
+      <c r="F2" s="398"/>
     </row>
     <row r="3" spans="1:16" s="176" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="376" t="s">
+      <c r="A3" s="399" t="s">
         <v>365</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
-      <c r="E3" s="376"/>
-      <c r="F3" s="376"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
     </row>
     <row r="4" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>226</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
@@ -14698,12 +14756,12 @@
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="1:16" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="377"/>
-      <c r="B5" s="377"/>
-      <c r="C5" s="377"/>
-      <c r="D5" s="377"/>
-      <c r="E5" s="377"/>
-      <c r="F5" s="377"/>
+      <c r="A5" s="400"/>
+      <c r="B5" s="400"/>
+      <c r="C5" s="400"/>
+      <c r="D5" s="400"/>
+      <c r="E5" s="400"/>
+      <c r="F5" s="400"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
@@ -14734,16 +14792,16 @@
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="1:16" s="140" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="449" t="s">
+      <c r="A7" s="448" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="449"/>
-      <c r="C7" s="448" t="s">
+      <c r="B7" s="448"/>
+      <c r="C7" s="447" t="s">
         <v>359</v>
       </c>
-      <c r="D7" s="448"/>
-      <c r="E7" s="448"/>
-      <c r="F7" s="448"/>
+      <c r="D7" s="447"/>
+      <c r="E7" s="447"/>
+      <c r="F7" s="447"/>
       <c r="G7" s="175"/>
       <c r="H7" s="175"/>
       <c r="I7" s="175"/>
@@ -15137,21 +15195,21 @@
       <c r="A36" s="153"/>
       <c r="B36" s="180"/>
       <c r="C36" s="173"/>
-      <c r="D36" s="380" t="s">
+      <c r="D36" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="E36" s="380"/>
-      <c r="F36" s="380"/>
+      <c r="E36" s="372"/>
+      <c r="F36" s="372"/>
     </row>
     <row r="37" spans="1:6" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="153"/>
       <c r="B37" s="153"/>
-      <c r="C37" s="396" t="s">
+      <c r="C37" s="373" t="s">
         <v>298</v>
       </c>
-      <c r="D37" s="396"/>
-      <c r="E37" s="396"/>
-      <c r="F37" s="396"/>
+      <c r="D37" s="373"/>
+      <c r="E37" s="373"/>
+      <c r="F37" s="373"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -15193,18 +15251,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A1" s="396" t="s">
+      <c r="A1" s="373" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="396"/>
-      <c r="C1" s="396"/>
-      <c r="D1" s="396"/>
-      <c r="E1" s="396"/>
-      <c r="F1" s="396"/>
-      <c r="G1" s="396"/>
-      <c r="H1" s="396"/>
-      <c r="I1" s="396"/>
-      <c r="J1" s="396"/>
+      <c r="B1" s="373"/>
+      <c r="C1" s="373"/>
+      <c r="D1" s="373"/>
+      <c r="E1" s="373"/>
+      <c r="F1" s="373"/>
+      <c r="G1" s="373"/>
+      <c r="H1" s="373"/>
+      <c r="I1" s="373"/>
+      <c r="J1" s="373"/>
     </row>
     <row r="2" spans="1:25" s="177" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="158"/>
@@ -15217,36 +15275,36 @@
       <c r="N2" s="215"/>
     </row>
     <row r="3" spans="1:25" s="177" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="448" t="s">
+      <c r="A3" s="447" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="448"/>
-      <c r="C3" s="448"/>
-      <c r="D3" s="448"/>
-      <c r="E3" s="448"/>
-      <c r="F3" s="448"/>
-      <c r="G3" s="448"/>
-      <c r="H3" s="448"/>
-      <c r="I3" s="448"/>
-      <c r="J3" s="448"/>
+      <c r="B3" s="447"/>
+      <c r="C3" s="447"/>
+      <c r="D3" s="447"/>
+      <c r="E3" s="447"/>
+      <c r="F3" s="447"/>
+      <c r="G3" s="447"/>
+      <c r="H3" s="447"/>
+      <c r="I3" s="447"/>
+      <c r="J3" s="447"/>
       <c r="K3" s="215"/>
       <c r="L3" s="215"/>
       <c r="M3" s="215"/>
       <c r="N3" s="215"/>
     </row>
     <row r="4" spans="1:25" s="177" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="448" t="s">
+      <c r="A4" s="447" t="s">
         <v>313</v>
       </c>
-      <c r="B4" s="448"/>
-      <c r="C4" s="448"/>
-      <c r="D4" s="448"/>
-      <c r="E4" s="448"/>
-      <c r="F4" s="448"/>
-      <c r="G4" s="448"/>
-      <c r="H4" s="448"/>
-      <c r="I4" s="448"/>
-      <c r="J4" s="448"/>
+      <c r="B4" s="447"/>
+      <c r="C4" s="447"/>
+      <c r="D4" s="447"/>
+      <c r="E4" s="447"/>
+      <c r="F4" s="447"/>
+      <c r="G4" s="447"/>
+      <c r="H4" s="447"/>
+      <c r="I4" s="447"/>
+      <c r="J4" s="447"/>
       <c r="K4" s="180"/>
       <c r="L4" s="180"/>
       <c r="M4" s="180"/>
@@ -15264,18 +15322,18 @@
       <c r="Y4" s="180"/>
     </row>
     <row r="5" spans="1:25" s="177" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="376" t="s">
+      <c r="A5" s="399" t="s">
         <v>366</v>
       </c>
-      <c r="B5" s="376"/>
-      <c r="C5" s="376"/>
-      <c r="D5" s="376"/>
-      <c r="E5" s="376"/>
-      <c r="F5" s="376"/>
-      <c r="G5" s="376"/>
-      <c r="H5" s="376"/>
-      <c r="I5" s="376"/>
-      <c r="J5" s="376"/>
+      <c r="B5" s="399"/>
+      <c r="C5" s="399"/>
+      <c r="D5" s="399"/>
+      <c r="E5" s="399"/>
+      <c r="F5" s="399"/>
+      <c r="G5" s="399"/>
+      <c r="H5" s="399"/>
+      <c r="I5" s="399"/>
+      <c r="J5" s="399"/>
       <c r="K5" s="180"/>
       <c r="L5" s="180"/>
       <c r="M5" s="180"/>
@@ -15293,40 +15351,40 @@
       <c r="Y5" s="180"/>
     </row>
     <row r="6" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="377" t="s">
+      <c r="A6" s="400" t="s">
         <v>255</v>
       </c>
-      <c r="B6" s="377"/>
-      <c r="C6" s="377"/>
-      <c r="D6" s="377"/>
-      <c r="E6" s="377"/>
-      <c r="F6" s="377"/>
-      <c r="G6" s="377"/>
-      <c r="H6" s="377"/>
-      <c r="I6" s="377"/>
-      <c r="J6" s="377"/>
+      <c r="B6" s="400"/>
+      <c r="C6" s="400"/>
+      <c r="D6" s="400"/>
+      <c r="E6" s="400"/>
+      <c r="F6" s="400"/>
+      <c r="G6" s="400"/>
+      <c r="H6" s="400"/>
+      <c r="I6" s="400"/>
+      <c r="J6" s="400"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="A7" s="377"/>
-      <c r="B7" s="377"/>
-      <c r="C7" s="377"/>
-      <c r="D7" s="377"/>
-      <c r="E7" s="377"/>
-      <c r="F7" s="377"/>
-      <c r="G7" s="377"/>
-      <c r="H7" s="377"/>
-      <c r="I7" s="377"/>
-      <c r="J7" s="377"/>
+      <c r="A7" s="400"/>
+      <c r="B7" s="400"/>
+      <c r="C7" s="400"/>
+      <c r="D7" s="400"/>
+      <c r="E7" s="400"/>
+      <c r="F7" s="400"/>
+      <c r="G7" s="400"/>
+      <c r="H7" s="400"/>
+      <c r="I7" s="400"/>
+      <c r="J7" s="400"/>
     </row>
     <row r="8" spans="1:25" s="177" customFormat="1" ht="54.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="449" t="s">
+      <c r="A8" s="448" t="s">
         <v>227</v>
       </c>
-      <c r="B8" s="449"/>
-      <c r="C8" s="449"/>
-      <c r="D8" s="449"/>
-      <c r="E8" s="449"/>
-      <c r="F8" s="449"/>
+      <c r="B8" s="448"/>
+      <c r="C8" s="448"/>
+      <c r="D8" s="448"/>
+      <c r="E8" s="448"/>
+      <c r="F8" s="448"/>
       <c r="G8" s="450" t="s">
         <v>360</v>
       </c>
@@ -15344,31 +15402,31 @@
       <c r="D9" s="179"/>
     </row>
     <row r="10" spans="1:25" s="201" customFormat="1" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="454" t="s">
+      <c r="A10" s="453" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="452" t="s">
+      <c r="B10" s="449" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="452" t="s">
+      <c r="C10" s="449" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="452" t="s">
+      <c r="D10" s="449" t="s">
         <v>156</v>
       </c>
-      <c r="E10" s="452"/>
-      <c r="F10" s="452"/>
-      <c r="G10" s="452"/>
-      <c r="H10" s="452" t="s">
+      <c r="E10" s="449"/>
+      <c r="F10" s="449"/>
+      <c r="G10" s="449"/>
+      <c r="H10" s="449" t="s">
         <v>157</v>
       </c>
-      <c r="I10" s="452"/>
-      <c r="J10" s="453"/>
+      <c r="I10" s="449"/>
+      <c r="J10" s="452"/>
     </row>
     <row r="11" spans="1:25" s="147" customFormat="1" ht="67.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="455"/>
-      <c r="B11" s="456"/>
-      <c r="C11" s="456"/>
+      <c r="A11" s="454"/>
+      <c r="B11" s="455"/>
+      <c r="C11" s="455"/>
       <c r="D11" s="58" t="s">
         <v>39</v>
       </c>
@@ -16093,18 +16151,18 @@
     </row>
     <row r="56" spans="1:11" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="457" t="s">
+      <c r="A57" s="456" t="s">
         <v>116</v>
       </c>
-      <c r="B57" s="457"/>
-      <c r="C57" s="457"/>
-      <c r="D57" s="457"/>
-      <c r="E57" s="457"/>
-      <c r="F57" s="457"/>
-      <c r="G57" s="457"/>
-      <c r="H57" s="457"/>
-      <c r="I57" s="457"/>
-      <c r="J57" s="457"/>
+      <c r="B57" s="456"/>
+      <c r="C57" s="456"/>
+      <c r="D57" s="456"/>
+      <c r="E57" s="456"/>
+      <c r="F57" s="456"/>
+      <c r="G57" s="456"/>
+      <c r="H57" s="456"/>
+      <c r="I57" s="456"/>
+      <c r="J57" s="456"/>
     </row>
     <row r="58" spans="1:11" s="177" customFormat="1" ht="18.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="39"/>
@@ -16136,25 +16194,25 @@
       <c r="C60" s="39"/>
       <c r="D60" s="39"/>
       <c r="E60" s="39"/>
-      <c r="F60" s="380" t="s">
+      <c r="F60" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="G60" s="380"/>
-      <c r="H60" s="380"/>
-      <c r="I60" s="380"/>
-      <c r="J60" s="380"/>
+      <c r="G60" s="372"/>
+      <c r="H60" s="372"/>
+      <c r="I60" s="372"/>
+      <c r="J60" s="372"/>
       <c r="K60" s="222"/>
     </row>
     <row r="61" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="173"/>
       <c r="E61" s="173"/>
-      <c r="F61" s="448" t="s">
+      <c r="F61" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="G61" s="448"/>
-      <c r="H61" s="448"/>
-      <c r="I61" s="448"/>
-      <c r="J61" s="448"/>
+      <c r="G61" s="447"/>
+      <c r="H61" s="447"/>
+      <c r="I61" s="447"/>
+      <c r="J61" s="447"/>
       <c r="K61" s="93"/>
     </row>
     <row r="62" spans="1:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -16179,13 +16237,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A8:F8"/>
     <mergeCell ref="B58:J58"/>
     <mergeCell ref="F60:J60"/>
     <mergeCell ref="F61:J61"/>
@@ -16197,6 +16248,13 @@
     <mergeCell ref="C10:C11"/>
     <mergeCell ref="A57:J57"/>
     <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A8:F8"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="159" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -16220,93 +16278,93 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="428" t="s">
+      <c r="A1" s="432" t="s">
         <v>278</v>
       </c>
-      <c r="B1" s="428"/>
-      <c r="C1" s="428"/>
-      <c r="D1" s="428"/>
-      <c r="E1" s="428"/>
-      <c r="F1" s="428"/>
-      <c r="G1" s="428"/>
-      <c r="H1" s="428"/>
-      <c r="I1" s="428"/>
+      <c r="B1" s="432"/>
+      <c r="C1" s="432"/>
+      <c r="D1" s="432"/>
+      <c r="E1" s="432"/>
+      <c r="F1" s="432"/>
+      <c r="G1" s="432"/>
+      <c r="H1" s="432"/>
+      <c r="I1" s="432"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="428" t="s">
+      <c r="A2" s="432" t="s">
         <v>367</v>
       </c>
-      <c r="B2" s="428"/>
-      <c r="C2" s="428"/>
-      <c r="D2" s="428"/>
-      <c r="E2" s="428"/>
-      <c r="F2" s="428"/>
-      <c r="G2" s="428"/>
-      <c r="H2" s="428"/>
-      <c r="I2" s="428"/>
+      <c r="B2" s="432"/>
+      <c r="C2" s="432"/>
+      <c r="D2" s="432"/>
+      <c r="E2" s="432"/>
+      <c r="F2" s="432"/>
+      <c r="G2" s="432"/>
+      <c r="H2" s="432"/>
+      <c r="I2" s="432"/>
     </row>
     <row r="3" spans="1:9" ht="89.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="380" t="s">
+      <c r="A3" s="372" t="s">
         <v>373</v>
       </c>
-      <c r="B3" s="380"/>
-      <c r="C3" s="380"/>
-      <c r="D3" s="380"/>
-      <c r="E3" s="380"/>
-      <c r="F3" s="380"/>
-      <c r="G3" s="380"/>
-      <c r="H3" s="380"/>
-      <c r="I3" s="380"/>
+      <c r="B3" s="372"/>
+      <c r="C3" s="372"/>
+      <c r="D3" s="372"/>
+      <c r="E3" s="372"/>
+      <c r="F3" s="372"/>
+      <c r="G3" s="372"/>
+      <c r="H3" s="372"/>
+      <c r="I3" s="372"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="429"/>
-      <c r="B4" s="429"/>
-      <c r="C4" s="429"/>
-      <c r="D4" s="429"/>
-      <c r="E4" s="429"/>
-      <c r="F4" s="429"/>
-      <c r="G4" s="429"/>
-      <c r="H4" s="429"/>
-      <c r="I4" s="429"/>
+      <c r="A4" s="433"/>
+      <c r="B4" s="433"/>
+      <c r="C4" s="433"/>
+      <c r="D4" s="433"/>
+      <c r="E4" s="433"/>
+      <c r="F4" s="433"/>
+      <c r="G4" s="433"/>
+      <c r="H4" s="433"/>
+      <c r="I4" s="433"/>
     </row>
     <row r="6" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="396" t="s">
+      <c r="A6" s="373" t="s">
         <v>287</v>
       </c>
-      <c r="B6" s="396"/>
-      <c r="C6" s="396"/>
-      <c r="D6" s="396"/>
-      <c r="E6" s="396" t="s">
+      <c r="B6" s="373"/>
+      <c r="C6" s="373"/>
+      <c r="D6" s="373"/>
+      <c r="E6" s="373" t="s">
         <v>325</v>
       </c>
-      <c r="F6" s="428"/>
-      <c r="G6" s="428"/>
-      <c r="H6" s="428"/>
-      <c r="I6" s="428"/>
+      <c r="F6" s="432"/>
+      <c r="G6" s="432"/>
+      <c r="H6" s="432"/>
+      <c r="I6" s="432"/>
     </row>
     <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="429" t="s">
+      <c r="A8" s="433" t="s">
         <v>361</v>
       </c>
-      <c r="B8" s="429"/>
-      <c r="C8" s="429"/>
-      <c r="D8" s="429"/>
-      <c r="E8" s="435" t="s">
+      <c r="B8" s="433"/>
+      <c r="C8" s="433"/>
+      <c r="D8" s="433"/>
+      <c r="E8" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="F8" s="435"/>
-      <c r="G8" s="435"/>
-      <c r="H8" s="435"/>
-      <c r="I8" s="435"/>
+      <c r="F8" s="442"/>
+      <c r="G8" s="442"/>
+      <c r="H8" s="442"/>
+      <c r="I8" s="442"/>
     </row>
     <row r="9" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="451" t="s">
         <v>368</v>
       </c>
-      <c r="B9" s="429"/>
-      <c r="C9" s="429"/>
-      <c r="D9" s="429"/>
+      <c r="B9" s="433"/>
+      <c r="C9" s="433"/>
+      <c r="D9" s="433"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C11" s="37" t="s">
@@ -16324,118 +16382,118 @@
       </c>
     </row>
     <row r="15" spans="1:9" ht="54" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="458" t="s">
+      <c r="A15" s="457" t="s">
         <v>323</v>
       </c>
-      <c r="B15" s="458"/>
-      <c r="C15" s="458"/>
-      <c r="D15" s="458"/>
-      <c r="E15" s="458"/>
-      <c r="F15" s="458"/>
-      <c r="G15" s="458"/>
-      <c r="H15" s="458"/>
-      <c r="I15" s="458"/>
+      <c r="B15" s="457"/>
+      <c r="C15" s="457"/>
+      <c r="D15" s="457"/>
+      <c r="E15" s="457"/>
+      <c r="F15" s="457"/>
+      <c r="G15" s="457"/>
+      <c r="H15" s="457"/>
+      <c r="I15" s="457"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="84"/>
-      <c r="B16" s="433" t="s">
+      <c r="B16" s="422" t="s">
         <v>369</v>
       </c>
-      <c r="C16" s="433"/>
-      <c r="D16" s="433"/>
-      <c r="E16" s="433"/>
-      <c r="F16" s="433"/>
-      <c r="G16" s="433"/>
-      <c r="H16" s="433"/>
-      <c r="I16" s="433"/>
+      <c r="C16" s="422"/>
+      <c r="D16" s="422"/>
+      <c r="E16" s="422"/>
+      <c r="F16" s="422"/>
+      <c r="G16" s="422"/>
+      <c r="H16" s="422"/>
+      <c r="I16" s="422"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="84"/>
-      <c r="B17" s="433" t="s">
+      <c r="B17" s="422" t="s">
         <v>370</v>
       </c>
-      <c r="C17" s="433"/>
-      <c r="D17" s="433"/>
-      <c r="E17" s="433"/>
-      <c r="F17" s="433"/>
-      <c r="G17" s="433"/>
-      <c r="H17" s="433"/>
-      <c r="I17" s="433"/>
+      <c r="C17" s="422"/>
+      <c r="D17" s="422"/>
+      <c r="E17" s="422"/>
+      <c r="F17" s="422"/>
+      <c r="G17" s="422"/>
+      <c r="H17" s="422"/>
+      <c r="I17" s="422"/>
     </row>
     <row r="18" spans="1:9" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="434" t="s">
+      <c r="A18" s="418" t="s">
         <v>324</v>
       </c>
-      <c r="B18" s="434"/>
-      <c r="C18" s="434"/>
-      <c r="D18" s="434"/>
-      <c r="E18" s="434"/>
-      <c r="F18" s="434"/>
-      <c r="G18" s="434"/>
-      <c r="H18" s="434"/>
-      <c r="I18" s="434"/>
+      <c r="B18" s="418"/>
+      <c r="C18" s="418"/>
+      <c r="D18" s="418"/>
+      <c r="E18" s="418"/>
+      <c r="F18" s="418"/>
+      <c r="G18" s="418"/>
+      <c r="H18" s="418"/>
+      <c r="I18" s="418"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="84"/>
-      <c r="B19" s="433" t="s">
+      <c r="B19" s="422" t="s">
         <v>371</v>
       </c>
-      <c r="C19" s="433"/>
-      <c r="D19" s="433"/>
-      <c r="E19" s="433"/>
-      <c r="F19" s="433"/>
-      <c r="G19" s="433"/>
-      <c r="H19" s="433"/>
-      <c r="I19" s="433"/>
+      <c r="C19" s="422"/>
+      <c r="D19" s="422"/>
+      <c r="E19" s="422"/>
+      <c r="F19" s="422"/>
+      <c r="G19" s="422"/>
+      <c r="H19" s="422"/>
+      <c r="I19" s="422"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="84"/>
-      <c r="B20" s="433" t="s">
+      <c r="B20" s="422" t="s">
         <v>282</v>
       </c>
-      <c r="C20" s="433"/>
-      <c r="D20" s="433"/>
-      <c r="E20" s="433"/>
-      <c r="F20" s="433"/>
-      <c r="G20" s="433"/>
-      <c r="H20" s="433"/>
-      <c r="I20" s="433"/>
+      <c r="C20" s="422"/>
+      <c r="D20" s="422"/>
+      <c r="E20" s="422"/>
+      <c r="F20" s="422"/>
+      <c r="G20" s="422"/>
+      <c r="H20" s="422"/>
+      <c r="I20" s="422"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B21" s="433" t="s">
+      <c r="B21" s="422" t="s">
         <v>281</v>
       </c>
-      <c r="C21" s="433"/>
-      <c r="D21" s="433"/>
-      <c r="E21" s="433"/>
-      <c r="F21" s="433"/>
-      <c r="G21" s="433"/>
-      <c r="H21" s="433"/>
-      <c r="I21" s="433"/>
+      <c r="C21" s="422"/>
+      <c r="D21" s="422"/>
+      <c r="E21" s="422"/>
+      <c r="F21" s="422"/>
+      <c r="G21" s="422"/>
+      <c r="H21" s="422"/>
+      <c r="I21" s="422"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="254" t="s">
         <v>284</v>
       </c>
-      <c r="E23" s="428" t="s">
+      <c r="E23" s="432" t="s">
         <v>283</v>
       </c>
-      <c r="F23" s="428"/>
-      <c r="G23" s="428"/>
-      <c r="H23" s="428"/>
-      <c r="I23" s="428"/>
+      <c r="F23" s="432"/>
+      <c r="G23" s="432"/>
+      <c r="H23" s="432"/>
+      <c r="I23" s="432"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="255" t="s">
         <v>285</v>
       </c>
-      <c r="E24" s="435" t="s">
+      <c r="E24" s="442" t="s">
         <v>297</v>
       </c>
-      <c r="F24" s="435"/>
-      <c r="G24" s="435"/>
-      <c r="H24" s="435"/>
-      <c r="I24" s="435"/>
+      <c r="F24" s="442"/>
+      <c r="G24" s="442"/>
+      <c r="H24" s="442"/>
+      <c r="I24" s="442"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="255" t="s">
@@ -16444,6 +16502,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="E6:I6"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
     <mergeCell ref="E23:I23"/>
     <mergeCell ref="E24:I24"/>
     <mergeCell ref="A18:I18"/>
@@ -16455,13 +16520,6 @@
     <mergeCell ref="B19:I19"/>
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
-    <mergeCell ref="E6:I6"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="A4:I4"/>
   </mergeCells>
   <pageMargins left="1.1811023622047245" right="0.78740157480314965" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="161" fitToHeight="0" orientation="portrait" useFirstPageNumber="1" r:id="rId1"/>
@@ -16489,32 +16547,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" s="56" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="440" t="s">
+      <c r="A1" s="434" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="440"/>
-      <c r="C1" s="440"/>
-      <c r="D1" s="440"/>
-      <c r="E1" s="440"/>
-      <c r="F1" s="440"/>
-      <c r="G1" s="440"/>
-      <c r="H1" s="440"/>
+      <c r="B1" s="434"/>
+      <c r="C1" s="434"/>
+      <c r="D1" s="434"/>
+      <c r="E1" s="434"/>
+      <c r="F1" s="434"/>
+      <c r="G1" s="434"/>
+      <c r="H1" s="434"/>
       <c r="I1" s="229"/>
       <c r="J1" s="229"/>
       <c r="K1" s="229"/>
       <c r="L1" s="229"/>
     </row>
     <row r="2" spans="1:23" s="56" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="440" t="s">
+      <c r="A2" s="434" t="s">
         <v>372</v>
       </c>
-      <c r="B2" s="440"/>
-      <c r="C2" s="440"/>
-      <c r="D2" s="440"/>
-      <c r="E2" s="440"/>
-      <c r="F2" s="440"/>
-      <c r="G2" s="440"/>
-      <c r="H2" s="440"/>
+      <c r="B2" s="434"/>
+      <c r="C2" s="434"/>
+      <c r="D2" s="434"/>
+      <c r="E2" s="434"/>
+      <c r="F2" s="434"/>
+      <c r="G2" s="434"/>
+      <c r="H2" s="434"/>
       <c r="I2" s="37"/>
       <c r="J2" s="37"/>
       <c r="K2" s="37"/>
@@ -16532,16 +16590,16 @@
       <c r="W2" s="37"/>
     </row>
     <row r="3" spans="1:23" s="56" customFormat="1" ht="72.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="376" t="s">
+      <c r="A3" s="399" t="s">
         <v>373</v>
       </c>
-      <c r="B3" s="441"/>
-      <c r="C3" s="441"/>
-      <c r="D3" s="441"/>
-      <c r="E3" s="441"/>
-      <c r="F3" s="441"/>
-      <c r="G3" s="441"/>
-      <c r="H3" s="441"/>
+      <c r="B3" s="435"/>
+      <c r="C3" s="435"/>
+      <c r="D3" s="435"/>
+      <c r="E3" s="435"/>
+      <c r="F3" s="435"/>
+      <c r="G3" s="435"/>
+      <c r="H3" s="435"/>
       <c r="I3" s="37"/>
       <c r="J3" s="37"/>
       <c r="K3" s="37"/>
@@ -16559,33 +16617,33 @@
       <c r="W3" s="37"/>
     </row>
     <row r="4" spans="1:23" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>254</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
     </row>
     <row r="5" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="429"/>
-      <c r="B5" s="429"/>
-      <c r="C5" s="429"/>
-      <c r="D5" s="429"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="429"/>
-      <c r="G5" s="429"/>
-      <c r="H5" s="429"/>
+      <c r="A5" s="433"/>
+      <c r="B5" s="433"/>
+      <c r="C5" s="433"/>
+      <c r="D5" s="433"/>
+      <c r="E5" s="433"/>
+      <c r="F5" s="433"/>
+      <c r="G5" s="433"/>
+      <c r="H5" s="433"/>
     </row>
     <row r="6" spans="1:23" s="56" customFormat="1" ht="54.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="447" t="s">
+      <c r="A6" s="441" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="447"/>
-      <c r="C6" s="447"/>
+      <c r="B6" s="441"/>
+      <c r="C6" s="441"/>
       <c r="D6" s="450" t="s">
         <v>360</v>
       </c>
@@ -16604,29 +16662,29 @@
       <c r="D7" s="230"/>
     </row>
     <row r="8" spans="1:23" s="57" customFormat="1" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="454" t="s">
+      <c r="A8" s="453" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="459" t="s">
+      <c r="B8" s="458" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="459" t="s">
+      <c r="C8" s="458" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="459" t="s">
+      <c r="D8" s="458" t="s">
         <v>159</v>
       </c>
-      <c r="E8" s="459"/>
-      <c r="F8" s="459"/>
-      <c r="G8" s="459" t="s">
+      <c r="E8" s="458"/>
+      <c r="F8" s="458"/>
+      <c r="G8" s="458" t="s">
         <v>256</v>
       </c>
-      <c r="H8" s="461"/>
+      <c r="H8" s="460"/>
     </row>
     <row r="9" spans="1:23" s="2" customFormat="1" ht="50.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="455"/>
-      <c r="B9" s="460"/>
-      <c r="C9" s="460"/>
+      <c r="A9" s="454"/>
+      <c r="B9" s="459"/>
+      <c r="C9" s="459"/>
       <c r="D9" s="58" t="s">
         <v>258</v>
       </c>
@@ -17138,30 +17196,30 @@
       <c r="B46" s="35"/>
       <c r="C46" s="35"/>
       <c r="D46" s="35"/>
-      <c r="E46" s="435" t="s">
+      <c r="E46" s="442" t="s">
         <v>306</v>
       </c>
-      <c r="F46" s="435"/>
-      <c r="G46" s="435"/>
-      <c r="H46" s="435"/>
+      <c r="F46" s="442"/>
+      <c r="G46" s="442"/>
+      <c r="H46" s="442"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B47" s="4"/>
-      <c r="E47" s="440" t="s">
+      <c r="E47" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="F47" s="440"/>
-      <c r="G47" s="440"/>
-      <c r="H47" s="440"/>
+      <c r="F47" s="434"/>
+      <c r="G47" s="434"/>
+      <c r="H47" s="434"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B48" s="4"/>
-      <c r="E48" s="429" t="s">
+      <c r="E48" s="433" t="s">
         <v>297</v>
       </c>
-      <c r="F48" s="429"/>
-      <c r="G48" s="429"/>
-      <c r="H48" s="429"/>
+      <c r="F48" s="433"/>
+      <c r="G48" s="433"/>
+      <c r="H48" s="433"/>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="37"/>
@@ -17232,6 +17290,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="E46:H46"/>
+    <mergeCell ref="E47:H47"/>
+    <mergeCell ref="E48:H48"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="G8:H8"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="A5:H5"/>
@@ -17241,12 +17305,6 @@
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="D6:H6"/>
     <mergeCell ref="A6:C6"/>
-    <mergeCell ref="E46:H46"/>
-    <mergeCell ref="E47:H47"/>
-    <mergeCell ref="E48:H48"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="G8:H8"/>
   </mergeCells>
   <pageMargins left="0.98425196850393704" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="162" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -17277,57 +17335,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A1" s="448" t="s">
+      <c r="A1" s="447" t="s">
         <v>133</v>
       </c>
-      <c r="B1" s="448"/>
-      <c r="C1" s="448"/>
-      <c r="D1" s="448"/>
-      <c r="E1" s="448"/>
-      <c r="F1" s="448"/>
-      <c r="G1" s="448"/>
-      <c r="H1" s="448"/>
-      <c r="I1" s="448"/>
-      <c r="J1" s="448"/>
-      <c r="K1" s="448"/>
-      <c r="L1" s="448"/>
-      <c r="M1" s="448"/>
+      <c r="B1" s="447"/>
+      <c r="C1" s="447"/>
+      <c r="D1" s="447"/>
+      <c r="E1" s="447"/>
+      <c r="F1" s="447"/>
+      <c r="G1" s="447"/>
+      <c r="H1" s="447"/>
+      <c r="I1" s="447"/>
+      <c r="J1" s="447"/>
+      <c r="K1" s="447"/>
+      <c r="L1" s="447"/>
+      <c r="M1" s="447"/>
       <c r="N1" s="93"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2" s="448" t="s">
+      <c r="A2" s="447" t="s">
         <v>376</v>
       </c>
-      <c r="B2" s="448"/>
-      <c r="C2" s="448"/>
-      <c r="D2" s="448"/>
-      <c r="E2" s="448"/>
-      <c r="F2" s="448"/>
-      <c r="G2" s="448"/>
-      <c r="H2" s="448"/>
-      <c r="I2" s="448"/>
-      <c r="J2" s="448"/>
-      <c r="K2" s="448"/>
-      <c r="L2" s="448"/>
-      <c r="M2" s="448"/>
+      <c r="B2" s="447"/>
+      <c r="C2" s="447"/>
+      <c r="D2" s="447"/>
+      <c r="E2" s="447"/>
+      <c r="F2" s="447"/>
+      <c r="G2" s="447"/>
+      <c r="H2" s="447"/>
+      <c r="I2" s="447"/>
+      <c r="J2" s="447"/>
+      <c r="K2" s="447"/>
+      <c r="L2" s="447"/>
+      <c r="M2" s="447"/>
       <c r="N2" s="93"/>
     </row>
     <row r="3" spans="1:28" ht="68.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="376" t="s">
+      <c r="A3" s="399" t="s">
         <v>375</v>
       </c>
-      <c r="B3" s="376"/>
-      <c r="C3" s="376"/>
-      <c r="D3" s="376"/>
-      <c r="E3" s="376"/>
-      <c r="F3" s="376"/>
-      <c r="G3" s="376"/>
-      <c r="H3" s="376"/>
-      <c r="I3" s="376"/>
-      <c r="J3" s="376"/>
-      <c r="K3" s="376"/>
-      <c r="L3" s="376"/>
-      <c r="M3" s="376"/>
+      <c r="B3" s="399"/>
+      <c r="C3" s="399"/>
+      <c r="D3" s="399"/>
+      <c r="E3" s="399"/>
+      <c r="F3" s="399"/>
+      <c r="G3" s="399"/>
+      <c r="H3" s="399"/>
+      <c r="I3" s="399"/>
+      <c r="J3" s="399"/>
+      <c r="K3" s="399"/>
+      <c r="L3" s="399"/>
+      <c r="M3" s="399"/>
       <c r="N3" s="180"/>
       <c r="O3" s="180"/>
       <c r="P3" s="180"/>
@@ -17345,54 +17403,54 @@
       <c r="AB3" s="180"/>
     </row>
     <row r="4" spans="1:28" s="32" customFormat="1" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="377" t="s">
+      <c r="A4" s="400" t="s">
         <v>220</v>
       </c>
-      <c r="B4" s="377"/>
-      <c r="C4" s="377"/>
-      <c r="D4" s="377"/>
-      <c r="E4" s="377"/>
-      <c r="F4" s="377"/>
-      <c r="G4" s="377"/>
-      <c r="H4" s="377"/>
-      <c r="I4" s="377"/>
-      <c r="J4" s="377"/>
-      <c r="K4" s="377"/>
-      <c r="L4" s="377"/>
-      <c r="M4" s="377"/>
+      <c r="B4" s="400"/>
+      <c r="C4" s="400"/>
+      <c r="D4" s="400"/>
+      <c r="E4" s="400"/>
+      <c r="F4" s="400"/>
+      <c r="G4" s="400"/>
+      <c r="H4" s="400"/>
+      <c r="I4" s="400"/>
+      <c r="J4" s="400"/>
+      <c r="K4" s="400"/>
+      <c r="L4" s="400"/>
+      <c r="M4" s="400"/>
       <c r="N4" s="34"/>
     </row>
     <row r="5" spans="1:28" s="32" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="377"/>
-      <c r="B5" s="377"/>
-      <c r="C5" s="377"/>
-      <c r="D5" s="377"/>
-      <c r="E5" s="377"/>
-      <c r="F5" s="377"/>
-      <c r="G5" s="377"/>
-      <c r="H5" s="377"/>
-      <c r="I5" s="377"/>
-      <c r="J5" s="377"/>
-      <c r="K5" s="377"/>
-      <c r="L5" s="377"/>
-      <c r="M5" s="377"/>
+      <c r="A5" s="400"/>
+      <c r="B5" s="400"/>
+      <c r="C5" s="400"/>
+      <c r="D5" s="400"/>
+      <c r="E5" s="400"/>
+      <c r="F5" s="400"/>
+      <c r="G5" s="400"/>
+      <c r="H5" s="400"/>
+      <c r="I5" s="400"/>
+      <c r="J5" s="400"/>
+      <c r="K5" s="400"/>
+      <c r="L5" s="400"/>
+      <c r="M5" s="400"/>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A6" s="449" t="s">
+      <c r="A6" s="448" t="s">
         <v>227</v>
       </c>
-      <c r="B6" s="449"/>
-      <c r="C6" s="449"/>
-      <c r="D6" s="449"/>
-      <c r="E6" s="449"/>
-      <c r="F6" s="449"/>
-      <c r="G6" s="449"/>
-      <c r="H6" s="449"/>
-      <c r="I6" s="449"/>
-      <c r="J6" s="449"/>
-      <c r="K6" s="449"/>
-      <c r="L6" s="449"/>
-      <c r="M6" s="449"/>
+      <c r="B6" s="448"/>
+      <c r="C6" s="448"/>
+      <c r="D6" s="448"/>
+      <c r="E6" s="448"/>
+      <c r="F6" s="448"/>
+      <c r="G6" s="448"/>
+      <c r="H6" s="448"/>
+      <c r="I6" s="448"/>
+      <c r="J6" s="448"/>
+      <c r="K6" s="448"/>
+      <c r="L6" s="448"/>
+      <c r="M6" s="448"/>
     </row>
     <row r="7" spans="1:28" s="32" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="6"/>
@@ -17405,52 +17463,52 @@
       <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:28" s="39" customFormat="1" ht="33.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="467" t="s">
+      <c r="A8" s="464" t="s">
         <v>0</v>
       </c>
-      <c r="B8" s="444" t="s">
+      <c r="B8" s="438" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="444" t="s">
+      <c r="C8" s="438" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="444" t="s">
+      <c r="D8" s="438" t="s">
         <v>2</v>
       </c>
-      <c r="E8" s="444" t="s">
+      <c r="E8" s="438" t="s">
         <v>193</v>
       </c>
-      <c r="F8" s="444" t="s">
+      <c r="F8" s="438" t="s">
         <v>290</v>
       </c>
-      <c r="G8" s="444" t="s">
+      <c r="G8" s="438" t="s">
         <v>118</v>
       </c>
-      <c r="H8" s="444" t="s">
+      <c r="H8" s="438" t="s">
         <v>43</v>
       </c>
-      <c r="I8" s="444" t="s">
+      <c r="I8" s="438" t="s">
         <v>374</v>
       </c>
-      <c r="J8" s="464" t="s">
+      <c r="J8" s="461" t="s">
         <v>276</v>
       </c>
-      <c r="K8" s="465"/>
-      <c r="L8" s="466"/>
-      <c r="M8" s="462" t="s">
+      <c r="K8" s="462"/>
+      <c r="L8" s="463"/>
+      <c r="M8" s="466" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="39" customFormat="1" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="468"/>
-      <c r="B9" s="445"/>
-      <c r="C9" s="445"/>
-      <c r="D9" s="445"/>
-      <c r="E9" s="445"/>
-      <c r="F9" s="445"/>
-      <c r="G9" s="445"/>
-      <c r="H9" s="445"/>
-      <c r="I9" s="445"/>
+      <c r="A9" s="465"/>
+      <c r="B9" s="439"/>
+      <c r="C9" s="439"/>
+      <c r="D9" s="439"/>
+      <c r="E9" s="439"/>
+      <c r="F9" s="439"/>
+      <c r="G9" s="439"/>
+      <c r="H9" s="439"/>
+      <c r="I9" s="439"/>
       <c r="J9" s="87" t="s">
         <v>274</v>
       </c>
@@ -17460,7 +17518,7 @@
       <c r="L9" s="87" t="s">
         <v>128</v>
       </c>
-      <c r="M9" s="463"/>
+      <c r="M9" s="467"/>
     </row>
     <row r="10" spans="1:28" s="45" customFormat="1" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="42">
@@ -17567,21 +17625,21 @@
     </row>
     <row r="15" spans="1:28" ht="17.399999999999999" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="457" t="s">
+      <c r="A16" s="456" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="457"/>
-      <c r="C16" s="457"/>
-      <c r="D16" s="457"/>
-      <c r="E16" s="457"/>
-      <c r="F16" s="457"/>
-      <c r="G16" s="457"/>
-      <c r="H16" s="457"/>
-      <c r="I16" s="457"/>
-      <c r="J16" s="457"/>
-      <c r="K16" s="457"/>
-      <c r="L16" s="457"/>
-      <c r="M16" s="457"/>
+      <c r="B16" s="456"/>
+      <c r="C16" s="456"/>
+      <c r="D16" s="456"/>
+      <c r="E16" s="456"/>
+      <c r="F16" s="456"/>
+      <c r="G16" s="456"/>
+      <c r="H16" s="456"/>
+      <c r="I16" s="456"/>
+      <c r="J16" s="456"/>
+      <c r="K16" s="456"/>
+      <c r="L16" s="456"/>
+      <c r="M16" s="456"/>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B17" s="450" t="s">
@@ -17636,26 +17694,26 @@
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C20" s="39"/>
       <c r="E20" s="39"/>
-      <c r="H20" s="380" t="s">
+      <c r="H20" s="372" t="s">
         <v>306</v>
       </c>
-      <c r="I20" s="380"/>
-      <c r="J20" s="380"/>
-      <c r="K20" s="380"/>
-      <c r="L20" s="380"/>
-      <c r="M20" s="380"/>
+      <c r="I20" s="372"/>
+      <c r="J20" s="372"/>
+      <c r="K20" s="372"/>
+      <c r="L20" s="372"/>
+      <c r="M20" s="372"/>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C21" s="173"/>
       <c r="E21" s="173"/>
-      <c r="H21" s="448" t="s">
+      <c r="H21" s="447" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="448"/>
-      <c r="J21" s="448"/>
-      <c r="K21" s="448"/>
-      <c r="L21" s="448"/>
-      <c r="M21" s="448"/>
+      <c r="I21" s="447"/>
+      <c r="J21" s="447"/>
+      <c r="K21" s="447"/>
+      <c r="L21" s="447"/>
+      <c r="M21" s="447"/>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="C22" s="173"/>
@@ -17670,7 +17728,7 @@
     </row>
   </sheetData>
   <customSheetViews>
-    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="I32" sqref="I32"/>
       <pageMargins left="0.45" right="0.36" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="74" orientation="landscape" useFirstPageNumber="1" r:id="rId1"/>
@@ -17678,7 +17736,7 @@
         <oddFooter>&amp;R&amp;P</oddFooter>
       </headerFooter>
     </customSheetView>
-    <customSheetView guid="{D46B2CF8-D2E7-4E6B-824D-42BE5A2B79B0}" showPageBreaks="1" printArea="1" view="pageLayout">
+    <customSheetView guid="{037F55BC-C5EE-4950-AD5F-1814D2FDF4CC}" showPageBreaks="1" printArea="1" view="pageLayout">
       <selection activeCell="I32" sqref="I32"/>
       <pageMargins left="0.45" right="0.36" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
       <pageSetup paperSize="9" firstPageNumber="74" orientation="landscape" useFirstPageNumber="1" r:id="rId2"/>
@@ -17688,6 +17746,16 @@
     </customSheetView>
   </customSheetViews>
   <mergeCells count="24">
+    <mergeCell ref="H21:M21"/>
+    <mergeCell ref="H22:M22"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="A6:M6"/>
+    <mergeCell ref="B17:M17"/>
+    <mergeCell ref="B18:M18"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="M8:M9"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="H20:M20"/>
     <mergeCell ref="A3:M3"/>
@@ -17702,16 +17770,6 @@
     <mergeCell ref="E8:E9"/>
     <mergeCell ref="F8:F9"/>
     <mergeCell ref="G8:G9"/>
-    <mergeCell ref="H21:M21"/>
-    <mergeCell ref="H22:M22"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="A6:M6"/>
-    <mergeCell ref="B17:M17"/>
-    <mergeCell ref="B18:M18"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="B19:M19"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="M8:M9"/>
   </mergeCells>
   <pageMargins left="0.98425196850393704" right="0.59055118110236227" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" firstPageNumber="164" fitToHeight="0" orientation="landscape" useFirstPageNumber="1" r:id="rId3"/>
